--- a/data/glassdoor_ratings.xlsx
+++ b/data/glassdoor_ratings.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:N72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
@@ -479,35 +479,40 @@
       </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
+          <t>CEO Approval</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
           <t>Total Reviews</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Diversity &amp; Inclusion</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Work/Life Balance</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Compensation and Benefits</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Culture &amp; Values</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Career Opportunities</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Senior Management</t>
         </is>
@@ -516,7 +521,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Global</t>
+          <t>ASUS - Global</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -531,41 +536,46 @@
         </is>
       </c>
       <c r="E2" s="2" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>90%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
         <is>
-          <t>5,442</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="n">
-        <v>4.4</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>1,491</t>
+        </is>
       </c>
       <c r="I2" s="2" t="n">
-        <v>3.9</v>
+        <v>3.3</v>
       </c>
       <c r="J2" s="2" t="n">
-        <v>4.4</v>
+        <v>3.2</v>
       </c>
       <c r="K2" s="2" t="n">
-        <v>4.3</v>
+        <v>3.2</v>
       </c>
       <c r="L2" s="2" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="M2" s="2" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Fremont, CA</t>
+          <t>ASUS - Fremont, CA</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
@@ -580,45 +590,50 @@
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
+          <t>Fremont, CA</t>
         </is>
       </c>
       <c r="E3" s="2" t="n">
-        <v>4.3</v>
+        <v>3.6</v>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>91%</t>
+          <t>51%</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="H3" s="2" t="n">
-        <v>4.2</v>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
       </c>
       <c r="I3" s="2" t="n">
-        <v>4.4</v>
+        <v>3.4</v>
       </c>
       <c r="J3" s="2" t="n">
-        <v>4.7</v>
+        <v>3</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>4.3</v>
+        <v>2.3</v>
       </c>
       <c r="L3" s="2" t="n">
-        <v>4.5</v>
+        <v>2.7</v>
       </c>
       <c r="M3" s="2" t="n">
-        <v>4.6</v>
+        <v>2.5</v>
+      </c>
+      <c r="N3" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Markham, ON</t>
+          <t>ASUS - Markham, ON</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
@@ -633,268 +648,263 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
+          <t>Markham, ON</t>
         </is>
       </c>
       <c r="E4" s="2" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>88%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="n">
-        <v>4.8</v>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="I4" s="2" t="n">
-        <v>4.5</v>
+        <v>1.1</v>
       </c>
       <c r="J4" s="2" t="n">
-        <v>5</v>
+        <v>1.6</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>4.8</v>
+        <v>2.1</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>4.6</v>
+        <v>1.1</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>4.8</v>
+        <v>1.3</v>
+      </c>
+      <c r="N4" s="2" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Hemel Hempstead, ENG</t>
+          <t>ASUS - Barcelona, CT</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead, ENG</t>
+          <t>Barcelona, CT</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Reading, ENG</t>
+          <t>Barcelona, CT</t>
         </is>
       </c>
       <c r="E5" s="2" t="n">
-        <v>4.3</v>
+        <v>2.4</v>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="n">
-        <v>5</v>
+          <t>33%</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="I5" s="2" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="J5" s="2" t="n">
-        <v>5</v>
+        <v>2.4</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>5</v>
+        <v>2.3</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>5</v>
+        <v>1.7</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
+      </c>
+      <c r="N5" s="2" t="n">
+        <v>1.7</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Ratingen, NW</t>
+          <t>ASUS - Budapest, BU</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Ratingen, NW</t>
+          <t>Budapest, BU</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Munich, BY</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I6" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="J6" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="K6" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="L6" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="M6" s="2" t="n">
-        <v>4.9</v>
-      </c>
+          <t>Budapest, BU</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr"/>
+      <c r="F6" s="2" t="inlineStr"/>
+      <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
+      <c r="I6" s="2" t="inlineStr"/>
+      <c r="J6" s="2" t="inlineStr"/>
+      <c r="K6" s="2" t="inlineStr"/>
+      <c r="L6" s="2" t="inlineStr"/>
+      <c r="M6" s="2" t="inlineStr"/>
+      <c r="N6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Mumbai, MH</t>
+          <t>ASUS - Emmen, DR</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Mumbai, MH</t>
+          <t>Emmen, DR</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, KA</t>
+          <t>Emmen, DR</t>
         </is>
       </c>
       <c r="E7" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>563</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="n">
-        <v>4.5</v>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="I7" s="2" t="n">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.4</v>
+        <v>4.8</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>4.5</v>
+        <v>2.9</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4.5</v>
+        <v>4.9</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>4.3</v>
+        <v>3</v>
+      </c>
+      <c r="N7" s="2" t="n">
+        <v>4</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Taipei, TPQ</t>
+          <t>ASUS - Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
+          <t>Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hsinchu, TXG</t>
+          <t>Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="E8" s="2" t="n">
-        <v>4.6</v>
+        <v>3.7</v>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="n">
-        <v>4</v>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
       </c>
       <c r="I8" s="2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="J8" s="2" t="n">
-        <v>4.4</v>
+        <v>3.8</v>
       </c>
       <c r="K8" s="2" t="n">
-        <v>5</v>
+        <v>2.8</v>
       </c>
       <c r="L8" s="2" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="M8" s="2" t="n">
-        <v>3.7</v>
+        <v>3</v>
+      </c>
+      <c r="N8" s="2" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>TSMC - Global</t>
+          <t>ASUS - Milan, LOM</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C9" s="2" t="inlineStr"/>
+          <t>Milan, LOM</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
+          <t>Milan, LOM</t>
         </is>
       </c>
       <c r="E9" s="2" t="n">
@@ -902,83 +912,3401 @@
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>46%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>2,135</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="n">
-        <v>2.8</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="I9" s="2" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
       </c>
       <c r="J9" s="2" t="n">
-        <v>3.8</v>
+        <v>2.4</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>2.6</v>
+        <v>1.5</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>3.5</v>
+        <v>2.4</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>2.7</v>
+        <v>3.3</v>
+      </c>
+      <c r="N9" s="2" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
+          <t>ASUS - Noisy-le-Grand, A8</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Noisy-le-Grand, A8</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Noisy-le-Grand, A8</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>22%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="L10" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M10" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N10" s="2" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="L11" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M11" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N11" s="2" t="n">
+        <v>2.5</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Bangkok, 10</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok, 10</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>Thailand</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Bangkok, 10</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L12" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N12" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Dubai, DU</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, DU</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>United Arab Emirates</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Dubai, DU</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L13" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="M13" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N13" s="2" t="n">
+        <v>2.2</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Jakarta, JK</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Jakarta, JK</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Jakarta, JK</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L14" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M14" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N14" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Kuala Lumpur, 14</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, 14</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>Malaysia</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Kuala Lumpur, 14</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="L15" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M15" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N15" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Manila, D9</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Manila, D9</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Manila, D9</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="L16" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M16" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N16" s="2" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L17" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M17" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N17" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Seoul, 11</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, 11</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>South Korea</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Seoul, 11</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="L18" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M18" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N18" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Singapore</t>
+        </is>
+      </c>
+      <c r="B19" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>37%</t>
+        </is>
+      </c>
+      <c r="G19" s="2" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="H19" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J19" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="K19" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L19" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M19" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N19" s="2" t="n">
+        <v>2.3</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="B20" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="C20" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>67%</t>
+        </is>
+      </c>
+      <c r="G20" s="2" t="inlineStr">
+        <is>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="H20" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J20" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K20" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L20" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M20" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N20" s="2" t="n">
+        <v>2.8</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Tokyo, 40</t>
+        </is>
+      </c>
+      <c r="B21" s="2" t="inlineStr">
+        <is>
+          <t>Tokyo, 40</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>Tokyo, 40</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr"/>
+      <c r="F21" s="2" t="inlineStr"/>
+      <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
+      <c r="I21" s="2" t="inlineStr"/>
+      <c r="J21" s="2" t="inlineStr"/>
+      <c r="K21" s="2" t="inlineStr"/>
+      <c r="L21" s="2" t="inlineStr"/>
+      <c r="M21" s="2" t="inlineStr"/>
+      <c r="N21" s="2" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Santiago, RM</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>Santiago, RM</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>Santiago, RM</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K22" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L22" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M22" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N22" s="2" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - São Paulo, SP</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, SP</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, SP</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="G23" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="J23" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="K23" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L23" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M23" s="2" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="N23" s="2" t="n">
+        <v>2.1</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>ASUS - Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>1%</t>
+        </is>
+      </c>
+      <c r="G24" s="2" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="J24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="K24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="L24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="M24" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="N24" s="2" t="n">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Acer - Global</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr"/>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="G25" s="2" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J25" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K25" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L25" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M25" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N25" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>AU Optronics - Global</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr"/>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F26" s="2" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
+      <c r="G26" s="2" t="inlineStr">
+        <is>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J26" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K26" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L26" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M26" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N26" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Compal Electronics - Global</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr"/>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="G27" s="2" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J27" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K27" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L27" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M27" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N27" s="2" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Compal Electronics - Emmen, DR</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>Emmen, DR</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>Hoofddorp, NH</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="G28" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H28" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J28" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="K28" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L28" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M28" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N28" s="2" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Compal Electronics - Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J29" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K29" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L29" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M29" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N29" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Dell Technologies - Global</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr"/>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>64%</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>36,332</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N30" s="2" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Dell Technologies - Fremont, CA</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>Aliso, CA</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr"/>
+      <c r="J31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K31" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N31" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Dell Technologies - Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, KA</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="G32" s="2" t="inlineStr">
+        <is>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>5,161</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J32" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K32" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L32" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M32" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N32" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Delta Electronics - Global</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr"/>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N33" s="2" t="n">
+        <v>3.2</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Delta Electronics - Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L34" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M34" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N34" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Google - Global</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr"/>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="G35" s="2" t="inlineStr">
+        <is>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>48,118</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J35" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K35" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="L35" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M35" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N35" s="2" t="n">
+        <v>3.9</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>HP Inc. - Global</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr"/>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="G36" s="2" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H36" s="2" t="inlineStr">
+        <is>
+          <t>9,431</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J36" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K36" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L36" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M36" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N36" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>HP Inc. - Fremont, CA</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>Boise, ID</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J37" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K37" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L37" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M37" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N37" s="2" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>HP Inc. - Barcelona, CT</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona, CT</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Spain</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>Barcelona, CT</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="G38" s="2" t="inlineStr"/>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J38" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K38" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L38" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="M38" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="N38" s="2" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>HP Inc. - Hemel Hempstead, ENG</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>Hemel Hempstead, ENG</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>Cambridge, ENG</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="inlineStr"/>
+      <c r="H39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr"/>
+      <c r="J39" s="2" t="inlineStr"/>
+      <c r="K39" s="2" t="inlineStr"/>
+      <c r="L39" s="2" t="inlineStr"/>
+      <c r="M39" s="2" t="inlineStr"/>
+      <c r="N39" s="2" t="inlineStr"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>HP Inc. - Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, KA</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>1,340</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J40" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K40" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="L40" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M40" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N40" s="2" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>HP Inc. - Singapore</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="inlineStr"/>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="J41" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K41" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L41" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M41" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N41" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>HP Inc. - Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="inlineStr"/>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="J42" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K42" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L42" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="M42" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N42" s="2" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Inventec - Global</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr"/>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="J43" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K43" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="L43" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M43" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N43" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo - Global</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr"/>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="inlineStr">
+        <is>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>3,519</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J44" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="K44" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L44" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M44" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N44" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo - Fremont, CA</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="F45" s="2" t="inlineStr">
+        <is>
+          <t>11%</t>
+        </is>
+      </c>
+      <c r="G45" s="2" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="J45" s="2" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="K45" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="L45" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="M45" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="N45" s="2" t="n">
+        <v>1.3</v>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo - Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>Stuttgart, BW</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F46" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="G46" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="J46" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K46" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L46" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="M46" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N46" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo - Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, KA</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="F47" s="2" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="G47" s="2" t="inlineStr">
+        <is>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="J47" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K47" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="L47" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="M47" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N47" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo - São Paulo, SP</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>São Paulo, SP</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Brazil</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>Campinas, SP</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr"/>
+      <c r="F48" s="2" t="inlineStr"/>
+      <c r="G48" s="2" t="inlineStr"/>
+      <c r="H48" s="2" t="inlineStr"/>
+      <c r="I48" s="2" t="inlineStr"/>
+      <c r="J48" s="2" t="inlineStr"/>
+      <c r="K48" s="2" t="inlineStr"/>
+      <c r="L48" s="2" t="inlineStr"/>
+      <c r="M48" s="2" t="inlineStr"/>
+      <c r="N48" s="2" t="inlineStr"/>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Lenovo - Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F49" s="2" t="inlineStr">
+        <is>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="G49" s="2" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="J49" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="K49" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L49" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="M49" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N49" s="2" t="n">
+        <v>2.6</v>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>MSI - Global</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr"/>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F50" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="G50" s="2" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="J50" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="K50" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N50" s="2" t="n">
+        <v>3.4</v>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA - Global</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr"/>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>5,442</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J51" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K51" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L51" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M51" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="N51" s="2" t="n">
+        <v>4.2</v>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA - Fremont, CA</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F52" s="2" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="G52" s="2" t="inlineStr">
+        <is>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J52" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K52" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L52" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M52" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="N52" s="2" t="n">
+        <v>4.6</v>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA - Markham, ON</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>Toronto, ON</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>88%</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J53" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K53" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L53" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M53" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N53" s="2" t="n">
+        <v>4.8</v>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA - Hemel Hempstead, ENG</t>
+        </is>
+      </c>
+      <c r="B54" s="2" t="inlineStr">
+        <is>
+          <t>Hemel Hempstead, ENG</t>
+        </is>
+      </c>
+      <c r="C54" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D54" s="2" t="inlineStr">
+        <is>
+          <t>Reading, ENG</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F54" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G54" s="2" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="H54" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J54" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M54" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="N54" s="2" t="n">
+        <v>4.4</v>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA - Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="B55" s="2" t="inlineStr">
+        <is>
+          <t>Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="C55" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D55" s="2" t="inlineStr">
+        <is>
+          <t>Munich, BY</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="F55" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G55" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H55" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
+      </c>
+      <c r="I55" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="J55" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="K55" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="L55" s="2" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="M55" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="N55" s="2" t="n">
+        <v>4.9</v>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA - Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="B56" s="2" t="inlineStr">
+        <is>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="C56" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
+      <c r="D56" s="2" t="inlineStr">
+        <is>
+          <t>Bengaluru, KA</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr"/>
+      <c r="F56" s="2" t="inlineStr"/>
+      <c r="G56" s="2" t="inlineStr"/>
+      <c r="H56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr"/>
+      <c r="J56" s="2" t="inlineStr"/>
+      <c r="K56" s="2" t="inlineStr"/>
+      <c r="L56" s="2" t="inlineStr"/>
+      <c r="M56" s="2" t="inlineStr"/>
+      <c r="N56" s="2" t="inlineStr"/>
+    </row>
+    <row r="57">
+      <c r="A57" s="2" t="inlineStr">
+        <is>
+          <t>NVIDIA - Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="B57" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="C57" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D57" s="2" t="inlineStr">
+        <is>
+          <t>Hsinchu, TXG</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="F57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="I57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J57" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K57" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="L57" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="M57" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N57" s="2" t="n">
+        <v>3.7</v>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="2" t="inlineStr">
+        <is>
+          <t>Pegatron - Global</t>
+        </is>
+      </c>
+      <c r="B58" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr"/>
+      <c r="D58" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F58" s="2" t="inlineStr">
+        <is>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="G58" s="2" t="inlineStr">
+        <is>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="H58" s="2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J58" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K58" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L58" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M58" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N58" s="2" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="2" t="inlineStr">
+        <is>
+          <t>Pegatron - Fremont, CA</t>
+        </is>
+      </c>
+      <c r="B59" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D59" s="2" t="inlineStr">
+        <is>
+          <t>Jeffersonville, IN</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr"/>
+      <c r="F59" s="2" t="inlineStr"/>
+      <c r="G59" s="2" t="inlineStr"/>
+      <c r="H59" s="2" t="inlineStr"/>
+      <c r="I59" s="2" t="inlineStr"/>
+      <c r="J59" s="2" t="inlineStr"/>
+      <c r="K59" s="2" t="inlineStr"/>
+      <c r="L59" s="2" t="inlineStr"/>
+      <c r="M59" s="2" t="inlineStr"/>
+      <c r="N59" s="2" t="inlineStr"/>
+    </row>
+    <row r="60">
+      <c r="A60" s="2" t="inlineStr">
+        <is>
+          <t>Quanta Computer - Global</t>
+        </is>
+      </c>
+      <c r="B60" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr"/>
+      <c r="D60" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="F60" s="2" t="inlineStr">
+        <is>
+          <t>50%</t>
+        </is>
+      </c>
+      <c r="G60" s="2" t="inlineStr">
+        <is>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H60" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J60" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="K60" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L60" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M60" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N60" s="2" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="2" t="inlineStr">
+        <is>
+          <t>Quanta Computer - Fremont, CA</t>
+        </is>
+      </c>
+      <c r="B61" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C61" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D61" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr"/>
+      <c r="F61" s="2" t="inlineStr"/>
+      <c r="G61" s="2" t="inlineStr"/>
+      <c r="H61" s="2" t="inlineStr"/>
+      <c r="I61" s="2" t="inlineStr"/>
+      <c r="J61" s="2" t="inlineStr"/>
+      <c r="K61" s="2" t="inlineStr"/>
+      <c r="L61" s="2" t="inlineStr"/>
+      <c r="M61" s="2" t="inlineStr"/>
+      <c r="N61" s="2" t="inlineStr"/>
+    </row>
+    <row r="62">
+      <c r="A62" s="2" t="inlineStr">
+        <is>
+          <t>Trend Micro - Global</t>
+        </is>
+      </c>
+      <c r="B62" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C62" s="2" t="inlineStr"/>
+      <c r="D62" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E62" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="F62" s="2" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="G62" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="H62" s="2" t="inlineStr">
+        <is>
+          <t>2,073</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J62" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K62" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="L62" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M62" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N62" s="2" t="n">
+        <v>3.3</v>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" s="2" t="inlineStr">
+        <is>
+          <t>Trend Micro - Fremont, CA</t>
+        </is>
+      </c>
+      <c r="B63" s="2" t="inlineStr">
+        <is>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
+      <c r="D63" s="2" t="inlineStr">
+        <is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="F63" s="2" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="G63" s="2" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="H63" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="J63" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="K63" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="L63" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="M63" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N63" s="2" t="n">
+        <v>3.1</v>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" s="2" t="inlineStr">
+        <is>
+          <t>Trend Micro - Markham, ON</t>
+        </is>
+      </c>
+      <c r="B64" s="2" t="inlineStr">
+        <is>
+          <t>Markham, ON</t>
+        </is>
+      </c>
+      <c r="C64" s="2" t="inlineStr">
+        <is>
+          <t>Canada</t>
+        </is>
+      </c>
+      <c r="D64" s="2" t="inlineStr">
+        <is>
+          <t>Kanata, ON</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F64" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G64" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H64" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="J64" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K64" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L64" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M64" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N64" s="2" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="2" t="inlineStr">
+        <is>
+          <t>Trend Micro - Hemel Hempstead, ENG</t>
+        </is>
+      </c>
+      <c r="B65" s="2" t="inlineStr">
+        <is>
+          <t>Hemel Hempstead, ENG</t>
+        </is>
+      </c>
+      <c r="C65" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
+      <c r="D65" s="2" t="inlineStr">
+        <is>
+          <t>London, ENG</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F65" s="2" t="inlineStr">
+        <is>
+          <t>85%</t>
+        </is>
+      </c>
+      <c r="G65" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H65" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="J65" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="L65" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M65" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="N65" s="2" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="2" t="inlineStr">
+        <is>
+          <t>Trend Micro - Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="B66" s="2" t="inlineStr">
+        <is>
+          <t>Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="C66" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
+      <c r="D66" s="2" t="inlineStr">
+        <is>
+          <t>Munich, BY</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="F66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="G66" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H66" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="J66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="K66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L66" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M66" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N66" s="2" t="n">
+        <v>3.6</v>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="2" t="inlineStr">
+        <is>
+          <t>Trend Micro - Tokyo, 40</t>
+        </is>
+      </c>
+      <c r="B67" s="2" t="inlineStr">
+        <is>
+          <t>Tokyo, 40</t>
+        </is>
+      </c>
+      <c r="C67" s="2" t="inlineStr">
+        <is>
+          <t>Japan</t>
+        </is>
+      </c>
+      <c r="D67" s="2" t="inlineStr">
+        <is>
+          <t>Tokyo, 40</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr"/>
+      <c r="F67" s="2" t="inlineStr"/>
+      <c r="G67" s="2" t="inlineStr"/>
+      <c r="H67" s="2" t="inlineStr"/>
+      <c r="I67" s="2" t="inlineStr"/>
+      <c r="J67" s="2" t="inlineStr"/>
+      <c r="K67" s="2" t="inlineStr"/>
+      <c r="L67" s="2" t="inlineStr"/>
+      <c r="M67" s="2" t="inlineStr"/>
+      <c r="N67" s="2" t="inlineStr"/>
+    </row>
+    <row r="68">
+      <c r="A68" s="2" t="inlineStr">
+        <is>
+          <t>TSMC - Global</t>
+        </is>
+      </c>
+      <c r="B68" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr"/>
+      <c r="D68" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="F68" s="2" t="inlineStr">
+        <is>
+          <t>46%</t>
+        </is>
+      </c>
+      <c r="G68" s="2" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="H68" s="2" t="inlineStr">
+        <is>
+          <t>2,135</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L68" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="M68" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="2" t="inlineStr">
+        <is>
           <t>TSMC - Taipei, TPQ</t>
         </is>
       </c>
-      <c r="B10" s="2" t="inlineStr">
+      <c r="B69" s="2" t="inlineStr">
         <is>
           <t>Taipei, TPQ</t>
         </is>
       </c>
-      <c r="C10" s="2" t="inlineStr">
+      <c r="C69" s="2" t="inlineStr">
         <is>
           <t>Taiwan</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="D69" s="2" t="inlineStr">
         <is>
           <t>Hsinchu, TXG</t>
         </is>
       </c>
-      <c r="E10" s="2" t="n">
+      <c r="E69" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F10" s="2" t="inlineStr">
+      <c r="F69" s="2" t="inlineStr">
         <is>
           <t>52%</t>
         </is>
       </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="G69" s="2" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="H69" s="2" t="inlineStr">
         <is>
           <t>613</t>
         </is>
       </c>
-      <c r="H10" s="2" t="n">
+      <c r="I69" s="2" t="n">
         <v>2.9</v>
       </c>
-      <c r="I10" s="2" t="n">
+      <c r="J69" s="2" t="n">
         <v>2.5</v>
       </c>
-      <c r="J10" s="2" t="n">
+      <c r="K69" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="K10" s="2" t="n">
+      <c r="L69" s="2" t="n">
         <v>2.8</v>
       </c>
-      <c r="L10" s="2" t="n">
+      <c r="M69" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="M10" s="2" t="n">
+      <c r="N69" s="2" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="2" t="inlineStr">
+        <is>
+          <t>Wistron - Global</t>
+        </is>
+      </c>
+      <c r="B70" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr"/>
+      <c r="D70" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="F70" s="2" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="J70" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="K70" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="L70" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M70" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="N70" s="2" t="n">
+        <v>2.7</v>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" s="2" t="inlineStr">
+        <is>
+          <t>Wistron - Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="B71" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
+      <c r="D71" s="2" t="inlineStr">
+        <is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="F71" s="2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="G71" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="H71" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="J71" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N71" s="2" t="n">
+        <v>2.9</v>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" s="2" t="inlineStr">
+        <is>
+          <t>Wiwynn - Global</t>
+        </is>
+      </c>
+      <c r="B72" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr"/>
+      <c r="D72" s="2" t="inlineStr">
+        <is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="F72" s="2" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="G72" s="2" t="inlineStr"/>
+      <c r="H72" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="J72" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="K72" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L72" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M72" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="N72" s="2" t="n">
         <v>2.9</v>
       </c>
     </row>

--- a/data/glassdoor_ratings.xlsx
+++ b/data/glassdoor_ratings.xlsx
@@ -429,21 +429,24 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N72"/>
+  <dimension ref="A1:O72"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
     <col width="22" customWidth="1" min="3" max="3"/>
-    <col width="10" customWidth="1" min="4" max="4"/>
-    <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="14" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="18" customWidth="1" min="8" max="8"/>
-    <col width="24" customWidth="1" min="9" max="9"/>
-    <col width="16" customWidth="1" min="10" max="10"/>
-    <col width="22" customWidth="1" min="11" max="11"/>
-    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="22" customWidth="1" min="4" max="4"/>
+    <col width="60" customWidth="1" min="5" max="5"/>
+    <col width="9" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="9" max="9"/>
+    <col width="23" customWidth="1" min="10" max="10"/>
+    <col width="19" customWidth="1" min="11" max="11"/>
+    <col width="27" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
+    <col width="22" customWidth="1" min="14" max="14"/>
+    <col width="19" customWidth="1" min="15" max="15"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -469,50 +472,55 @@
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
+          <t>Review URL</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
           <t>Overall</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>Recommend</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>CEO Approval</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
+      <c r="I1" s="1" t="inlineStr">
         <is>
           <t>Total Reviews</t>
         </is>
       </c>
-      <c r="I1" s="1" t="inlineStr">
+      <c r="J1" s="1" t="inlineStr">
         <is>
           <t>Diversity &amp; Inclusion</t>
         </is>
       </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="K1" s="1" t="inlineStr">
         <is>
           <t>Work/Life Balance</t>
         </is>
       </c>
-      <c r="K1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>Compensation and Benefits</t>
         </is>
       </c>
-      <c r="L1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>Culture &amp; Values</t>
         </is>
       </c>
-      <c r="M1" s="1" t="inlineStr">
+      <c r="N1" s="1" t="inlineStr">
         <is>
           <t>Career Opportunities</t>
         </is>
       </c>
-      <c r="N1" s="1" t="inlineStr">
+      <c r="O1" s="1" t="inlineStr">
         <is>
           <t>Senior Management</t>
         </is>
@@ -521,7 +529,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Global</t>
+          <t>Acer - Global</t>
         </is>
       </c>
       <c r="B2" s="2" t="inlineStr">
@@ -535,987 +543,1069 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E2" s="2" t="n">
+      <c r="E2" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Acer-Group-Reviews-E3802.htm</t>
+        </is>
+      </c>
+      <c r="F2" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="G2" s="2" t="inlineStr">
+        <is>
+          <t>63%</t>
+        </is>
+      </c>
+      <c r="H2" s="2" t="inlineStr">
+        <is>
+          <t>73%</t>
+        </is>
+      </c>
+      <c r="I2" s="2" t="inlineStr">
+        <is>
+          <t>510</t>
+        </is>
+      </c>
+      <c r="J2" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="F2" s="2" t="inlineStr">
-        <is>
-          <t>57%</t>
-        </is>
-      </c>
-      <c r="G2" s="2" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
-      </c>
-      <c r="H2" s="2" t="inlineStr">
-        <is>
-          <t>1,491</t>
-        </is>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>3.2</v>
-      </c>
       <c r="K2" s="2" t="n">
-        <v>3.2</v>
+        <v>3.8</v>
       </c>
       <c r="L2" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="N2" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O2" s="2" t="n">
         <v>3.1</v>
-      </c>
-      <c r="M2" s="2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N2" s="2" t="n">
-        <v>2.8</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Fremont, CA</t>
+          <t>Dell Technologies - Global</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
-        </is>
-      </c>
-      <c r="C3" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr"/>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
-        </is>
-      </c>
-      <c r="E3" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F3" s="2" t="inlineStr">
-        <is>
-          <t>51%</t>
-        </is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Dell-Technologies-Reviews-E1327.htm</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="n">
+        <v>3.7</v>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>64%</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>79</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="n">
+          <t>70%</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>36,332</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="N3" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="J3" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="K3" s="2" t="n">
-        <v>2.3</v>
-      </c>
-      <c r="L3" s="2" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="M3" s="2" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="N3" s="2" t="n">
-        <v>3</v>
+      <c r="O3" s="2" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Markham, ON</t>
+          <t>Dell Technologies - Fremont, CA</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>Markham, ON</t>
+          <t>Fremont, CA</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Markham, ON</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr"/>
+          <t>Aliso, CA</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Dell-Technologies-Aliso-Reviews-EI_IE1327.0,17_IL.18,23_IC3789361.htm</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>1.1</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>1.6</v>
-      </c>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr"/>
       <c r="K4" s="2" t="n">
-        <v>2.1</v>
+        <v>5</v>
       </c>
       <c r="L4" s="2" t="n">
-        <v>1.1</v>
+        <v>5</v>
       </c>
       <c r="M4" s="2" t="n">
-        <v>1.3</v>
+        <v>4</v>
       </c>
       <c r="N4" s="2" t="n">
-        <v>1.3</v>
+        <v>4</v>
+      </c>
+      <c r="O4" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Barcelona, CT</t>
+          <t>Dell Technologies - Mumbai, MH</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>Barcelona, CT</t>
+          <t>Mumbai, MH</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Barcelona, CT</t>
-        </is>
-      </c>
-      <c r="E5" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>33%</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
+          <t>Bengaluru, KA</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Dell-Technologies-Bengaluru-Reviews-EI_IE1327.0,17_IL.18,27_IC2940587.htm</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="n">
-        <v>1.7</v>
+          <t>86%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>5,161</t>
+        </is>
       </c>
       <c r="J5" s="2" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="L5" s="2" t="n">
-        <v>1.7</v>
+        <v>3.5</v>
       </c>
       <c r="M5" s="2" t="n">
-        <v>2.3</v>
+        <v>4.1</v>
       </c>
       <c r="N5" s="2" t="n">
-        <v>1.7</v>
+        <v>3.7</v>
+      </c>
+      <c r="O5" s="2" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Budapest, BU</t>
+          <t>HP Inc. - Global</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>Budapest, BU</t>
-        </is>
-      </c>
-      <c r="C6" s="2" t="inlineStr">
-        <is>
-          <t>Hungary</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr"/>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Budapest, BU</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr"/>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr"/>
-      <c r="H6" s="2" t="inlineStr"/>
-      <c r="I6" s="2" t="inlineStr"/>
-      <c r="J6" s="2" t="inlineStr"/>
-      <c r="K6" s="2" t="inlineStr"/>
-      <c r="L6" s="2" t="inlineStr"/>
-      <c r="M6" s="2" t="inlineStr"/>
-      <c r="N6" s="2" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/HP-Inc-Reviews-E1093161.htm</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>9,431</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K6" s="2" t="n">
+        <v>4.1</v>
+      </c>
+      <c r="L6" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="M6" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N6" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O6" s="2" t="n">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Emmen, DR</t>
+          <t>HP Inc. - Fremont, CA</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>Emmen, DR</t>
+          <t>Fremont, CA</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Emmen, DR</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F7" s="2" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
+          <t>Boise, ID</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/HP-Inc-Boise-Reviews-EI_IE1093161.0,6_IL.7,12_IC1127927.htm</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="n">
+        <v>3.4</v>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="H7" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I7" s="2" t="n">
-        <v>5</v>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr"/>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
       </c>
       <c r="J7" s="2" t="n">
-        <v>4.8</v>
+        <v>4.2</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2.9</v>
+        <v>3.9</v>
       </c>
       <c r="L7" s="2" t="n">
-        <v>4.9</v>
+        <v>3.4</v>
       </c>
       <c r="M7" s="2" t="n">
-        <v>3</v>
+        <v>3.6</v>
       </c>
       <c r="N7" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
+      </c>
+      <c r="O7" s="2" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Hemel Hempstead, ENG</t>
+          <t>HP Inc. - Barcelona, CT</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead, ENG</t>
+          <t>Barcelona, CT</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead, ENG</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
+          <t>Barcelona, CT</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/HP-Inc-Barcelona-Reviews-EI_IE1093161.0,6_IL.7,16_IC2547194.htm</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="n">
-        <v>4.5</v>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr"/>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>225</t>
+        </is>
       </c>
       <c r="J8" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="L8" s="2" t="n">
         <v>3.8</v>
       </c>
-      <c r="K8" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="L8" s="2" t="n">
-        <v>4.3</v>
-      </c>
       <c r="M8" s="2" t="n">
-        <v>3</v>
+        <v>4.1</v>
       </c>
       <c r="N8" s="2" t="n">
         <v>3.8</v>
       </c>
+      <c r="O8" s="2" t="n">
+        <v>3.6</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Milan, LOM</t>
+          <t>HP Inc. - Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>Milan, LOM</t>
+          <t>Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>Italy</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>Milan, LOM</t>
-        </is>
-      </c>
-      <c r="E9" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F9" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
+          <t>Cambridge, ENG</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/HP-Inc-Cambridge-Reviews-EI_IE1093161.0,6_IL.7,16_IC2662516.htm</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="n">
+        <v>4.2</v>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H9" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I9" s="2" t="n">
-        <v>3.3</v>
+          <t>21%</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr"/>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J9" s="2" t="n">
-        <v>2.4</v>
+        <v>5</v>
       </c>
       <c r="K9" s="2" t="n">
-        <v>1.5</v>
+        <v>3.4</v>
       </c>
       <c r="L9" s="2" t="n">
-        <v>2.4</v>
+        <v>3.4</v>
       </c>
       <c r="M9" s="2" t="n">
-        <v>3.3</v>
+        <v>3.4</v>
       </c>
       <c r="N9" s="2" t="n">
-        <v>3.3</v>
+        <v>2.6</v>
+      </c>
+      <c r="O9" s="2" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Noisy-le-Grand, A8</t>
+          <t>HP Inc. - Mumbai, MH</t>
         </is>
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>Noisy-le-Grand, A8</t>
+          <t>Mumbai, MH</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>France</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>Noisy-le-Grand, A8</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="n">
-        <v>2.4</v>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>22%</t>
-        </is>
+          <t>Bengaluru, KA</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/HP-Inc-Bengaluru-Reviews-EI_IE1093161.0,6_IL.7,16_IC2940587.htm</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>23%</t>
+          <t>81%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="n">
-        <v>2.8</v>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>1,340</t>
+        </is>
       </c>
       <c r="J10" s="2" t="n">
-        <v>2.2</v>
+        <v>4.2</v>
       </c>
       <c r="K10" s="2" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="L10" s="2" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
       </c>
       <c r="M10" s="2" t="n">
-        <v>2.1</v>
+        <v>4.2</v>
       </c>
       <c r="N10" s="2" t="n">
-        <v>2.3</v>
+        <v>3.6</v>
+      </c>
+      <c r="O10" s="2" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Ratingen, NW</t>
+          <t>HP Inc. - Singapore</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
         <is>
-          <t>Ratingen, NW</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>Ratingen, NW</t>
-        </is>
-      </c>
-      <c r="E11" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>97%</t>
-        </is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/HP-Inc-Singapore-Reviews-EI_IE1093161.0,6_IL.7,16_IC3235921.htm</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="n">
+        <v>3.9</v>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I11" s="2" t="n">
-        <v>1.4</v>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>547</t>
+        </is>
       </c>
       <c r="J11" s="2" t="n">
-        <v>3</v>
+        <v>4.3</v>
       </c>
       <c r="K11" s="2" t="n">
-        <v>1.6</v>
+        <v>4.2</v>
       </c>
       <c r="L11" s="2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="M11" s="2" t="n">
-        <v>2.3</v>
+        <v>4.2</v>
       </c>
       <c r="N11" s="2" t="n">
-        <v>2.5</v>
+        <v>3.4</v>
+      </c>
+      <c r="O11" s="2" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Bangkok, 10</t>
+          <t>HP Inc. - Taipei, TPQ</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
         <is>
-          <t>Bangkok, 10</t>
+          <t>Taipei, TPQ</t>
         </is>
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Thailand</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>Bangkok, 10</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>79%</t>
-        </is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/HP-Inc-Taipei-Reviews-EI_IE1093161.0,6_IL.7,13_IC3271041.htm</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="n">
+        <v>4.3</v>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="n">
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
         <v>4.5</v>
       </c>
-      <c r="J12" s="2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="K12" s="2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="L12" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M12" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="N12" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="M12" s="2" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="N12" s="2" t="n">
-        <v>3.4</v>
+      <c r="O12" s="2" t="n">
+        <v>3.6</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Dubai, DU</t>
+          <t>MSI - Global</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
         <is>
-          <t>Dubai, DU</t>
-        </is>
-      </c>
-      <c r="C13" s="2" t="inlineStr">
-        <is>
-          <t>United Arab Emirates</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr"/>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>Dubai, DU</t>
-        </is>
-      </c>
-      <c r="E13" s="2" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
-        <is>
-          <t>3%</t>
-        </is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/MSI-Reviews-E1273104.htm</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>75%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="n">
-        <v>2.3</v>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>63</t>
+        </is>
       </c>
       <c r="J13" s="2" t="n">
-        <v>1.9</v>
+        <v>3.9</v>
       </c>
       <c r="K13" s="2" t="n">
-        <v>1.7</v>
+        <v>3.8</v>
       </c>
       <c r="L13" s="2" t="n">
-        <v>2.2</v>
+        <v>3.5</v>
       </c>
       <c r="M13" s="2" t="n">
-        <v>2.3</v>
+        <v>3.8</v>
       </c>
       <c r="N13" s="2" t="n">
-        <v>2.2</v>
+        <v>3.3</v>
+      </c>
+      <c r="O13" s="2" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Jakarta, JK</t>
+          <t>Quanta Computer - Global</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
         <is>
-          <t>Jakarta, JK</t>
-        </is>
-      </c>
-      <c r="C14" s="2" t="inlineStr">
-        <is>
-          <t>Indonesia</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr"/>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>Jakarta, JK</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Quanta-Computer-Reviews-E11939.htm</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>50%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="n">
-        <v>4.6</v>
+          <t>54%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>570</t>
+        </is>
       </c>
       <c r="J14" s="2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="K14" s="2" t="n">
-        <v>4.3</v>
+        <v>2.6</v>
       </c>
       <c r="L14" s="2" t="n">
-        <v>4.2</v>
+        <v>3</v>
       </c>
       <c r="M14" s="2" t="n">
-        <v>3.8</v>
+        <v>2.6</v>
       </c>
       <c r="N14" s="2" t="n">
-        <v>4</v>
+        <v>3.1</v>
+      </c>
+      <c r="O14" s="2" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Kuala Lumpur, 14</t>
+          <t>Quanta Computer - Fremont, CA</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, 14</t>
+          <t>Fremont, CA</t>
         </is>
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Malaysia</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>Kuala Lumpur, 14</t>
-        </is>
-      </c>
-      <c r="E15" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F15" s="2" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
-      </c>
-      <c r="G15" s="2" t="inlineStr"/>
-      <c r="H15" s="2" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I15" s="2" t="n">
-        <v>4</v>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Quanta-Computer-Fremont-Reviews-EI_IE11939.0,15_IL.16,23_IC1147355.htm</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>3%</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
       </c>
       <c r="J15" s="2" t="n">
-        <v>4</v>
+        <v>2.6</v>
       </c>
       <c r="K15" s="2" t="n">
-        <v>4.9</v>
+        <v>2.7</v>
       </c>
       <c r="L15" s="2" t="n">
-        <v>4</v>
+        <v>2.3</v>
       </c>
       <c r="M15" s="2" t="n">
-        <v>5</v>
+        <v>2.6</v>
       </c>
       <c r="N15" s="2" t="n">
-        <v>3</v>
+        <v>2.1</v>
+      </c>
+      <c r="O15" s="2" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Manila, D9</t>
+          <t>Wistron - Global</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
         <is>
-          <t>Manila, D9</t>
-        </is>
-      </c>
-      <c r="C16" s="2" t="inlineStr">
-        <is>
-          <t>Philippines</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr"/>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>Manila, D9</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Wistron-Reviews-E15218.htm</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="n">
-        <v>3.9</v>
+          <t>83%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>710</t>
+        </is>
       </c>
       <c r="J16" s="2" t="n">
-        <v>1.7</v>
+        <v>3</v>
       </c>
       <c r="K16" s="2" t="n">
-        <v>4.8</v>
+        <v>3.1</v>
       </c>
       <c r="L16" s="2" t="n">
-        <v>3.9</v>
+        <v>2.8</v>
       </c>
       <c r="M16" s="2" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="N16" s="2" t="n">
-        <v>3.9</v>
+        <v>3.1</v>
+      </c>
+      <c r="O16" s="2" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Mumbai, MH</t>
+          <t>Wistron - Taipei, TPQ</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
         <is>
-          <t>Mumbai, MH</t>
+          <t>Taipei, TPQ</t>
         </is>
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>Mumbai, MH</t>
-        </is>
-      </c>
-      <c r="E17" s="2" t="n">
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Wistron-Taipei-Reviews-EI_IE15218.0,7_IL.8,14_IC3271041.htm</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>95%</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>216</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I17" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="J17" s="2" t="n">
-        <v>3.7</v>
-      </c>
       <c r="K17" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L17" s="2" t="n">
         <v>3</v>
       </c>
-      <c r="L17" s="2" t="n">
-        <v>3.1</v>
-      </c>
       <c r="M17" s="2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="N17" s="2" t="n">
-        <v>3</v>
+        <v>3.5</v>
+      </c>
+      <c r="O17" s="2" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Seoul, 11</t>
+          <t>AU Optronics - Global</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>Seoul, 11</t>
-        </is>
-      </c>
-      <c r="C18" s="2" t="inlineStr">
-        <is>
-          <t>South Korea</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr"/>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Seoul, 11</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F18" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G18" s="2" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/AU-Optronics-Reviews-E16126.htm</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>61%</t>
+        </is>
+      </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I18" s="2" t="n">
-        <v>3</v>
+          <t>76%</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
       </c>
       <c r="J18" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K18" s="2" t="n">
-        <v>2</v>
+        <v>3.7</v>
       </c>
       <c r="L18" s="2" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="M18" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="N18" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="O18" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Singapore</t>
+          <t>Delta Electronics - Global</t>
         </is>
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="C19" s="2" t="inlineStr">
-        <is>
-          <t>Singapore</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C19" s="2" t="inlineStr"/>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="n">
-        <v>2.8</v>
-      </c>
-      <c r="F19" s="2" t="inlineStr">
-        <is>
-          <t>37%</t>
-        </is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Delta-Electronics-Reviews-E41146.htm</t>
+        </is>
+      </c>
+      <c r="F19" s="2" t="n">
+        <v>3.6</v>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44%</t>
+          <t>66%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="I19" s="2" t="n">
-        <v>3.1</v>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
       </c>
       <c r="J19" s="2" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="K19" s="2" t="n">
-        <v>2.7</v>
+        <v>3.5</v>
       </c>
       <c r="L19" s="2" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M19" s="2" t="n">
-        <v>2.6</v>
+        <v>3.4</v>
       </c>
       <c r="N19" s="2" t="n">
-        <v>2.3</v>
+        <v>3.5</v>
+      </c>
+      <c r="O19" s="2" t="n">
+        <v>3.2</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Taipei, TPQ</t>
+          <t>Delta Electronics - Taipei, TPQ</t>
         </is>
       </c>
       <c r="B20" s="2" t="inlineStr">
@@ -1533,807 +1623,922 @@
           <t>Taipei, TPQ</t>
         </is>
       </c>
-      <c r="E20" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F20" s="2" t="inlineStr">
-        <is>
-          <t>67%</t>
-        </is>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Delta-Electronics-Taipei-Reviews-EI_IE41146.0,17_IL.18,24_IC3271041.htm</t>
+        </is>
+      </c>
+      <c r="F20" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>98%</t>
+          <t>93%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>524</t>
-        </is>
-      </c>
-      <c r="I20" s="2" t="n">
-        <v>3.3</v>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="I20" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
       </c>
       <c r="J20" s="2" t="n">
-        <v>3.8</v>
+        <v>3.5</v>
       </c>
       <c r="K20" s="2" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L20" s="2" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="M20" s="2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="N20" s="2" t="n">
-        <v>2.8</v>
+        <v>3.9</v>
+      </c>
+      <c r="O20" s="2" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Tokyo, 40</t>
+          <t>Inventec - Global</t>
         </is>
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
-          <t>Tokyo, 40</t>
-        </is>
-      </c>
-      <c r="C21" s="2" t="inlineStr">
-        <is>
-          <t>Japan</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr"/>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>Tokyo, 40</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
-      <c r="G21" s="2" t="inlineStr"/>
-      <c r="H21" s="2" t="inlineStr"/>
-      <c r="I21" s="2" t="inlineStr"/>
-      <c r="J21" s="2" t="inlineStr"/>
-      <c r="K21" s="2" t="inlineStr"/>
-      <c r="L21" s="2" t="inlineStr"/>
-      <c r="M21" s="2" t="inlineStr"/>
-      <c r="N21" s="2" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Inventec-Reviews-E13485.htm</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="G21" s="2" t="inlineStr">
+        <is>
+          <t>56%</t>
+        </is>
+      </c>
+      <c r="H21" s="2" t="inlineStr">
+        <is>
+          <t>77%</t>
+        </is>
+      </c>
+      <c r="I21" s="2" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="J21" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="K21" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L21" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="M21" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N21" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="O21" s="2" t="n">
+        <v>3.1</v>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Santiago, RM</t>
+          <t>NVIDIA - Global</t>
         </is>
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>Santiago, RM</t>
-        </is>
-      </c>
-      <c r="C22" s="2" t="inlineStr">
-        <is>
-          <t>Chile</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr"/>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>Santiago, RM</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F22" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G22" s="2" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/NVIDIA-Reviews-E7633.htm</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G22" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I22" s="2" t="n">
-        <v>5</v>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="I22" s="2" t="inlineStr">
+        <is>
+          <t>5,442</t>
+        </is>
       </c>
       <c r="J22" s="2" t="n">
-        <v>3</v>
+        <v>4.4</v>
       </c>
       <c r="K22" s="2" t="n">
-        <v>3</v>
+        <v>3.9</v>
       </c>
       <c r="L22" s="2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="M22" s="2" t="n">
-        <v>5</v>
+        <v>4.3</v>
       </c>
       <c r="N22" s="2" t="n">
-        <v>4</v>
+        <v>4.3</v>
+      </c>
+      <c r="O22" s="2" t="n">
+        <v>4.2</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
         <is>
-          <t>ASUS - São Paulo, SP</t>
+          <t>NVIDIA - Fremont, CA</t>
         </is>
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
+          <t>Fremont, CA</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
-        </is>
-      </c>
-      <c r="E23" s="2" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="F23" s="2" t="inlineStr">
-        <is>
-          <t>55%</t>
-        </is>
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/NVIDIA-Austin-Reviews-EI_IE7633.0,6_IL.7,13_IC1139761.htm</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="n">
+        <v>4.3</v>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>91%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="I23" s="2" t="n">
-        <v>3.1</v>
+          <t>91%</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
       </c>
       <c r="J23" s="2" t="n">
-        <v>2.4</v>
+        <v>4.2</v>
       </c>
       <c r="K23" s="2" t="n">
-        <v>3.7</v>
+        <v>4.4</v>
       </c>
       <c r="L23" s="2" t="n">
-        <v>2.3</v>
+        <v>4.7</v>
       </c>
       <c r="M23" s="2" t="n">
-        <v>1.6</v>
+        <v>4.3</v>
       </c>
       <c r="N23" s="2" t="n">
-        <v>2.1</v>
+        <v>4.5</v>
+      </c>
+      <c r="O23" s="2" t="n">
+        <v>4.6</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
         <is>
-          <t>ASUS - Sydney, NSW</t>
+          <t>NVIDIA - Markham, ON</t>
         </is>
       </c>
       <c r="B24" s="2" t="inlineStr">
         <is>
-          <t>Sydney, NSW</t>
+          <t>Markham, ON</t>
         </is>
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>Sydney, NSW</t>
-        </is>
-      </c>
-      <c r="E24" s="2" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="F24" s="2" t="inlineStr">
-        <is>
-          <t>1%</t>
-        </is>
+          <t>Toronto, ON</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/NVIDIA-Toronto-Reviews-EI_IE7633.0,6_IL.7,14_IC2281069.htm</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="n">
+        <v>4.9</v>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>53%</t>
+          <t>88%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="I24" s="2" t="n">
-        <v>1</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="inlineStr">
+        <is>
+          <t>23</t>
+        </is>
       </c>
       <c r="J24" s="2" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="K24" s="2" t="n">
-        <v>1</v>
+        <v>4.5</v>
       </c>
       <c r="L24" s="2" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="M24" s="2" t="n">
-        <v>1</v>
+        <v>4.8</v>
       </c>
       <c r="N24" s="2" t="n">
-        <v>1</v>
+        <v>4.6</v>
+      </c>
+      <c r="O24" s="2" t="n">
+        <v>4.8</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
         <is>
-          <t>Acer - Global</t>
+          <t>NVIDIA - Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="B25" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C25" s="2" t="inlineStr"/>
+          <t>Hemel Hempstead, ENG</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>United Kingdom</t>
+        </is>
+      </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E25" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="F25" s="2" t="inlineStr">
-        <is>
-          <t>63%</t>
-        </is>
+          <t>Reading, ENG</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/NVIDIA-Reading-Reviews-EI_IE7633.0,6_IL.7,14_IC2675152.htm</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="n">
+        <v>4.3</v>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>73%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>510</t>
-        </is>
-      </c>
-      <c r="I25" s="2" t="n">
-        <v>3.6</v>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J25" s="2" t="n">
-        <v>3.8</v>
+        <v>5</v>
       </c>
       <c r="K25" s="2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L25" s="2" t="n">
-        <v>3.6</v>
+        <v>5</v>
       </c>
       <c r="M25" s="2" t="n">
-        <v>3.4</v>
+        <v>5</v>
       </c>
       <c r="N25" s="2" t="n">
-        <v>3.1</v>
+        <v>5</v>
+      </c>
+      <c r="O25" s="2" t="n">
+        <v>4.4</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
         <is>
-          <t>AU Optronics - Global</t>
+          <t>NVIDIA - Ratingen, NW</t>
         </is>
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C26" s="2" t="inlineStr"/>
+          <t>Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E26" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F26" s="2" t="inlineStr">
-        <is>
-          <t>61%</t>
-        </is>
+          <t>Munich, BY</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/NVIDIA-Munich-Reviews-EI_IE7633.0,6_IL.7,13_IC4990924.htm</t>
+        </is>
+      </c>
+      <c r="F26" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>76%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="I26" s="2" t="n">
-        <v>3.3</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="J26" s="2" t="n">
-        <v>3.7</v>
+        <v>4.8</v>
       </c>
       <c r="K26" s="2" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="L26" s="2" t="n">
-        <v>3.3</v>
+        <v>5</v>
       </c>
       <c r="M26" s="2" t="n">
-        <v>3.4</v>
+        <v>4.9</v>
       </c>
       <c r="N26" s="2" t="n">
-        <v>3</v>
+        <v>4.6</v>
+      </c>
+      <c r="O26" s="2" t="n">
+        <v>4.9</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
         <is>
-          <t>Compal Electronics - Global</t>
+          <t>NVIDIA - Mumbai, MH</t>
         </is>
       </c>
       <c r="B27" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C27" s="2" t="inlineStr"/>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E27" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F27" s="2" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
+          <t>Bengaluru, KA</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/NVIDIA-Bengaluru-Reviews-EI_IE7633.0,6_IL.7,16_IC2940587.htm</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="n">
+        <v>4.5</v>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>95%</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="I27" s="2" t="n">
-        <v>3.5</v>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="inlineStr">
+        <is>
+          <t>563</t>
+        </is>
       </c>
       <c r="J27" s="2" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="K27" s="2" t="n">
-        <v>3.6</v>
+        <v>4.1</v>
       </c>
       <c r="L27" s="2" t="n">
-        <v>3.4</v>
+        <v>4.4</v>
       </c>
       <c r="M27" s="2" t="n">
-        <v>3.5</v>
+        <v>4.5</v>
       </c>
       <c r="N27" s="2" t="n">
-        <v>3.2</v>
+        <v>4.5</v>
+      </c>
+      <c r="O27" s="2" t="n">
+        <v>4.3</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
         <is>
-          <t>Compal Electronics - Emmen, DR</t>
+          <t>NVIDIA - Taipei, TPQ</t>
         </is>
       </c>
       <c r="B28" s="2" t="inlineStr">
         <is>
-          <t>Emmen, DR</t>
+          <t>Taipei, TPQ</t>
         </is>
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
-          <t>Netherlands</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D28" s="2" t="inlineStr">
         <is>
-          <t>Hoofddorp, NH</t>
-        </is>
-      </c>
-      <c r="E28" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F28" s="2" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
+          <t>Hsinchu, TXG</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/NVIDIA-Hsinchu-Reviews-EI_IE7633.0,6_IL.7,14_IC4915323.htm</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="n">
+        <v>4.6</v>
       </c>
       <c r="G28" s="2" t="inlineStr">
         <is>
-          <t>99%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H28" s="2" t="inlineStr">
         <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="I28" s="2" t="n">
-        <v>3.6</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I28" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J28" s="2" t="n">
-        <v>3.3</v>
+        <v>4</v>
       </c>
       <c r="K28" s="2" t="n">
-        <v>3.6</v>
+        <v>4</v>
       </c>
       <c r="L28" s="2" t="n">
-        <v>3.1</v>
+        <v>4.4</v>
       </c>
       <c r="M28" s="2" t="n">
-        <v>2.3</v>
+        <v>5</v>
       </c>
       <c r="N28" s="2" t="n">
-        <v>2.6</v>
+        <v>4.4</v>
+      </c>
+      <c r="O28" s="2" t="n">
+        <v>3.7</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
         <is>
-          <t>Compal Electronics - Taipei, TPQ</t>
+          <t>Trend Micro - Global</t>
         </is>
       </c>
       <c r="B29" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
-        </is>
-      </c>
-      <c r="C29" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr"/>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
-        </is>
-      </c>
-      <c r="E29" s="2" t="n">
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Trend-Micro-Inc-Reviews-E8983.htm</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G29" s="2" t="inlineStr">
+        <is>
+          <t>71%</t>
+        </is>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="inlineStr">
+        <is>
+          <t>2,073</t>
+        </is>
+      </c>
+      <c r="J29" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F29" s="2" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="G29" s="2" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="H29" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="I29" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J29" s="2" t="n">
-        <v>4.2</v>
-      </c>
       <c r="K29" s="2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="L29" s="2" t="n">
-        <v>3.2</v>
+        <v>3.3</v>
       </c>
       <c r="M29" s="2" t="n">
-        <v>3.9</v>
+        <v>4</v>
       </c>
       <c r="N29" s="2" t="n">
-        <v>3.4</v>
+        <v>3.6</v>
+      </c>
+      <c r="O29" s="2" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
         <is>
-          <t>Dell Technologies - Global</t>
+          <t>Trend Micro - Fremont, CA</t>
         </is>
       </c>
       <c r="B30" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C30" s="2" t="inlineStr"/>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="D30" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E30" s="2" t="n">
+          <t>Austin, TX</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Trend-Micro-Inc-Austin-Reviews-EI_IE8983.0,15_IL.16,22_IC1139761.htm</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="G30" s="2" t="inlineStr">
+        <is>
+          <t>72%</t>
+        </is>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>68%</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="inlineStr">
+        <is>
+          <t>36</t>
+        </is>
+      </c>
+      <c r="J30" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="K30" s="2" t="n">
+        <v>4.7</v>
+      </c>
+      <c r="L30" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="M30" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N30" s="2" t="n">
         <v>3.7</v>
       </c>
-      <c r="F30" s="2" t="inlineStr">
-        <is>
-          <t>64%</t>
-        </is>
-      </c>
-      <c r="G30" s="2" t="inlineStr">
-        <is>
-          <t>70%</t>
-        </is>
-      </c>
-      <c r="H30" s="2" t="inlineStr">
-        <is>
-          <t>36,332</t>
-        </is>
-      </c>
-      <c r="I30" s="2" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="J30" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="K30" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="L30" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="M30" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N30" s="2" t="n">
-        <v>3.3</v>
+      <c r="O30" s="2" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
         <is>
-          <t>Dell Technologies - Fremont, CA</t>
+          <t>Trend Micro - Markham, ON</t>
         </is>
       </c>
       <c r="B31" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
+          <t>Markham, ON</t>
         </is>
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>Aliso, CA</t>
-        </is>
-      </c>
-      <c r="E31" s="2" t="n">
+          <t>Kanata, ON</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Trend-Micro-Inc-Kanata-Reviews-EI_IE8983.0,15_IL.16,22_IC2282818.htm</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="n">
+        <v>3.3</v>
+      </c>
+      <c r="G31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J31" s="2" t="n">
         <v>4</v>
-      </c>
-      <c r="F31" s="2" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="G31" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H31" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I31" s="2" t="inlineStr"/>
-      <c r="J31" s="2" t="n">
-        <v>5</v>
       </c>
       <c r="K31" s="2" t="n">
         <v>5</v>
       </c>
       <c r="L31" s="2" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="M31" s="2" t="n">
         <v>4</v>
       </c>
       <c r="N31" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="O31" s="2" t="n">
         <v>3</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
         <is>
-          <t>Dell Technologies - Mumbai, MH</t>
+          <t>Trend Micro - Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="B32" s="2" t="inlineStr">
         <is>
-          <t>Mumbai, MH</t>
+          <t>Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D32" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, KA</t>
-        </is>
-      </c>
-      <c r="E32" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F32" s="2" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
+          <t>London, ENG</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Trend-Micro-Inc-London-Reviews-EI_IE8983.0,15_IL.16,22_IC2671300.htm</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="n">
+        <v>3.6</v>
       </c>
       <c r="G32" s="2" t="inlineStr">
         <is>
-          <t>86%</t>
+          <t>85%</t>
         </is>
       </c>
       <c r="H32" s="2" t="inlineStr">
         <is>
-          <t>5,161</t>
-        </is>
-      </c>
-      <c r="I32" s="2" t="n">
-        <v>4.2</v>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="J32" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="K32" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K32" s="2" t="n">
-        <v>3.5</v>
-      </c>
       <c r="L32" s="2" t="n">
-        <v>4.1</v>
+        <v>3.7</v>
       </c>
       <c r="M32" s="2" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="N32" s="2" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
+      </c>
+      <c r="O32" s="2" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
         <is>
-          <t>Delta Electronics - Global</t>
+          <t>Trend Micro - Ratingen, NW</t>
         </is>
       </c>
       <c r="B33" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C33" s="2" t="inlineStr"/>
+          <t>Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Germany</t>
+        </is>
+      </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E33" s="2" t="n">
+          <t>Munich, BY</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Trend-Micro-Inc-Munich-Reviews-EI_IE8983.0,15_IL.16,22_IC4990924.htm</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J33" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="K33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="L33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="M33" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N33" s="2" t="n">
         <v>3.6</v>
       </c>
-      <c r="F33" s="2" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
-      </c>
-      <c r="G33" s="2" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="H33" s="2" t="inlineStr">
-        <is>
-          <t>754</t>
-        </is>
-      </c>
-      <c r="I33" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J33" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="K33" s="2" t="n">
+      <c r="O33" s="2" t="n">
         <v>3.6</v>
-      </c>
-      <c r="L33" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="M33" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N33" s="2" t="n">
-        <v>3.2</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
         <is>
-          <t>Delta Electronics - Taipei, TPQ</t>
+          <t>Trend Micro - Tokyo, 40</t>
         </is>
       </c>
       <c r="B34" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
+          <t>Tokyo, 40</t>
         </is>
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D34" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
-        </is>
-      </c>
-      <c r="E34" s="2" t="n">
+          <t>Tokyo, 40</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Trend-Micro-Inc-Tokyo-Reviews-EI_IE8983.0,15_IL.16,21_IC2851580.htm</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="n">
+        <v>4.4</v>
+      </c>
+      <c r="G34" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="J34" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="K34" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="L34" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="F34" s="2" t="inlineStr">
-        <is>
-          <t>93%</t>
-        </is>
-      </c>
-      <c r="G34" s="2" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
-      </c>
-      <c r="H34" s="2" t="inlineStr">
-        <is>
-          <t>118</t>
-        </is>
-      </c>
-      <c r="I34" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="J34" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K34" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="L34" s="2" t="n">
-        <v>3.2</v>
-      </c>
       <c r="M34" s="2" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="N34" s="2" t="n">
-        <v>3.4</v>
+        <v>4.5</v>
+      </c>
+      <c r="O34" s="2" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
         <is>
-          <t>Google - Global</t>
+          <t>Wiwynn - Global</t>
         </is>
       </c>
       <c r="B35" s="2" t="inlineStr">
@@ -2347,47 +2552,48 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E35" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F35" s="2" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Wiwynn-Reviews-E1161475.htm</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="n">
+        <v>3.5</v>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>82%</t>
-        </is>
-      </c>
-      <c r="H35" s="2" t="inlineStr">
-        <is>
-          <t>48,118</t>
-        </is>
-      </c>
-      <c r="I35" s="2" t="n">
-        <v>4.4</v>
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="H35" s="2" t="inlineStr"/>
+      <c r="I35" s="2" t="inlineStr">
+        <is>
+          <t>86</t>
+        </is>
       </c>
       <c r="J35" s="2" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
       </c>
       <c r="K35" s="2" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="L35" s="2" t="n">
-        <v>4.2</v>
+        <v>3.5</v>
       </c>
       <c r="M35" s="2" t="n">
-        <v>4.2</v>
+        <v>3.1</v>
       </c>
       <c r="N35" s="2" t="n">
-        <v>3.9</v>
+        <v>3.5</v>
+      </c>
+      <c r="O35" s="2" t="n">
+        <v>2.9</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
         <is>
-          <t>HP Inc. - Global</t>
+          <t>ASUS - Global</t>
         </is>
       </c>
       <c r="B36" s="2" t="inlineStr">
@@ -2401,47 +2607,52 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E36" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F36" s="2" t="inlineStr">
-        <is>
-          <t>74%</t>
-        </is>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Reviews-E40093.htm</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="n">
+        <v>3.6</v>
       </c>
       <c r="G36" s="2" t="inlineStr">
         <is>
-          <t>59%</t>
+          <t>57%</t>
         </is>
       </c>
       <c r="H36" s="2" t="inlineStr">
         <is>
-          <t>9,431</t>
-        </is>
-      </c>
-      <c r="I36" s="2" t="n">
-        <v>4.2</v>
+          <t>75%</t>
+        </is>
+      </c>
+      <c r="I36" s="2" t="inlineStr">
+        <is>
+          <t>1,491</t>
+        </is>
       </c>
       <c r="J36" s="2" t="n">
-        <v>4.1</v>
+        <v>3.3</v>
       </c>
       <c r="K36" s="2" t="n">
-        <v>3.5</v>
+        <v>3.2</v>
       </c>
       <c r="L36" s="2" t="n">
-        <v>4</v>
+        <v>3.2</v>
       </c>
       <c r="M36" s="2" t="n">
-        <v>3.5</v>
+        <v>3.1</v>
       </c>
       <c r="N36" s="2" t="n">
-        <v>3.4</v>
+        <v>3.1</v>
+      </c>
+      <c r="O36" s="2" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
         <is>
-          <t>HP Inc. - Fremont, CA</t>
+          <t>ASUS - Fremont, CA</t>
         </is>
       </c>
       <c r="B37" s="2" t="inlineStr">
@@ -2456,1272 +2667,1479 @@
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>Boise, ID</t>
-        </is>
-      </c>
-      <c r="E37" s="2" t="n">
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Fremont-Reviews-EI_IE40093.0,4_IL.5,12_IC1147355.htm</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G37" s="2" t="inlineStr">
+        <is>
+          <t>51%</t>
+        </is>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>97%</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="inlineStr">
+        <is>
+          <t>79</t>
+        </is>
+      </c>
+      <c r="J37" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="F37" s="2" t="inlineStr">
-        <is>
-          <t>54%</t>
-        </is>
-      </c>
-      <c r="G37" s="2" t="inlineStr"/>
-      <c r="H37" s="2" t="inlineStr">
-        <is>
-          <t>180</t>
-        </is>
-      </c>
-      <c r="I37" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J37" s="2" t="n">
-        <v>3.9</v>
-      </c>
       <c r="K37" s="2" t="n">
-        <v>3.4</v>
+        <v>3</v>
       </c>
       <c r="L37" s="2" t="n">
-        <v>3.6</v>
+        <v>2.3</v>
       </c>
       <c r="M37" s="2" t="n">
-        <v>3.3</v>
+        <v>2.7</v>
       </c>
       <c r="N37" s="2" t="n">
-        <v>2.7</v>
+        <v>2.5</v>
+      </c>
+      <c r="O37" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
         <is>
-          <t>HP Inc. - Barcelona, CT</t>
+          <t>ASUS - Markham, ON</t>
         </is>
       </c>
       <c r="B38" s="2" t="inlineStr">
         <is>
-          <t>Barcelona, CT</t>
+          <t>Markham, ON</t>
         </is>
       </c>
       <c r="C38" s="2" t="inlineStr">
         <is>
-          <t>Spain</t>
+          <t>Canada</t>
         </is>
       </c>
       <c r="D38" s="2" t="inlineStr">
         <is>
-          <t>Barcelona, CT</t>
-        </is>
-      </c>
-      <c r="E38" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F38" s="2" t="inlineStr">
-        <is>
-          <t>94%</t>
-        </is>
-      </c>
-      <c r="G38" s="2" t="inlineStr"/>
-      <c r="H38" s="2" t="inlineStr">
-        <is>
-          <t>225</t>
-        </is>
-      </c>
-      <c r="I38" s="2" t="n">
-        <v>4.2</v>
+          <t>Markham, ON</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Markham-Reviews-EI_IE40093.0,4_IL.5,12_IC2280736.htm</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="G38" s="2" t="inlineStr">
+        <is>
+          <t>0%</t>
+        </is>
+      </c>
+      <c r="H38" s="2" t="inlineStr"/>
+      <c r="I38" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="J38" s="2" t="n">
-        <v>4.3</v>
+        <v>1.1</v>
       </c>
       <c r="K38" s="2" t="n">
-        <v>3.8</v>
+        <v>1.6</v>
       </c>
       <c r="L38" s="2" t="n">
-        <v>4.1</v>
+        <v>2.1</v>
       </c>
       <c r="M38" s="2" t="n">
-        <v>3.8</v>
+        <v>1.1</v>
       </c>
       <c r="N38" s="2" t="n">
-        <v>3.6</v>
+        <v>1.3</v>
+      </c>
+      <c r="O38" s="2" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
         <is>
-          <t>HP Inc. - Hemel Hempstead, ENG</t>
+          <t>ASUS - Barcelona, CT</t>
         </is>
       </c>
       <c r="B39" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead, ENG</t>
+          <t>Barcelona, CT</t>
         </is>
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Spain</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>Cambridge, ENG</t>
-        </is>
-      </c>
-      <c r="E39" s="2" t="inlineStr"/>
-      <c r="F39" s="2" t="inlineStr"/>
-      <c r="G39" s="2" t="inlineStr"/>
+          <t>Barcelona, CT</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Barcelona-Reviews-EI_IE40093.0,4_IL.5,14_IC2547194.htm</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="G39" s="2" t="inlineStr">
+        <is>
+          <t>33%</t>
+        </is>
+      </c>
       <c r="H39" s="2" t="inlineStr"/>
-      <c r="I39" s="2" t="inlineStr"/>
-      <c r="J39" s="2" t="inlineStr"/>
-      <c r="K39" s="2" t="inlineStr"/>
-      <c r="L39" s="2" t="inlineStr"/>
-      <c r="M39" s="2" t="inlineStr"/>
-      <c r="N39" s="2" t="inlineStr"/>
+      <c r="I39" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J39" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="K39" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="L39" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M39" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="N39" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="O39" s="2" t="n">
+        <v>1.7</v>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
-          <t>HP Inc. - Mumbai, MH</t>
+          <t>ASUS - Budapest, BU</t>
         </is>
       </c>
       <c r="B40" s="2" t="inlineStr">
         <is>
-          <t>Mumbai, MH</t>
+          <t>Budapest, BU</t>
         </is>
       </c>
       <c r="C40" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Hungary</t>
         </is>
       </c>
       <c r="D40" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, KA</t>
-        </is>
-      </c>
-      <c r="E40" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F40" s="2" t="inlineStr">
-        <is>
-          <t>81%</t>
-        </is>
-      </c>
-      <c r="G40" s="2" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
-      </c>
-      <c r="H40" s="2" t="inlineStr">
-        <is>
-          <t>1,340</t>
-        </is>
-      </c>
-      <c r="I40" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="J40" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K40" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="L40" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M40" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="N40" s="2" t="n">
-        <v>3.6</v>
-      </c>
+          <t>Budapest, BU</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Budapest-Reviews-EI_IE40093.0,4_IL.5,13_IC3125126.htm</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr"/>
+      <c r="G40" s="2" t="inlineStr"/>
+      <c r="H40" s="2" t="inlineStr"/>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+      <c r="K40" s="2" t="inlineStr"/>
+      <c r="L40" s="2" t="inlineStr"/>
+      <c r="M40" s="2" t="inlineStr"/>
+      <c r="N40" s="2" t="inlineStr"/>
+      <c r="O40" s="2" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
         <is>
-          <t>HP Inc. - Singapore</t>
+          <t>ASUS - Emmen, DR</t>
         </is>
       </c>
       <c r="B41" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Emmen, DR</t>
         </is>
       </c>
       <c r="C41" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
+          <t>Netherlands</t>
         </is>
       </c>
       <c r="D41" s="2" t="inlineStr">
         <is>
-          <t>Singapore</t>
-        </is>
-      </c>
-      <c r="E41" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F41" s="2" t="inlineStr">
-        <is>
-          <t>69%</t>
-        </is>
-      </c>
+          <t>Emmen, DR</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Emmen-Reviews-EI_IE40093.0,4_IL.5,10_IC3060162.htm</t>
+        </is>
+      </c>
+      <c r="F41" s="2" t="inlineStr"/>
       <c r="G41" s="2" t="inlineStr"/>
-      <c r="H41" s="2" t="inlineStr">
-        <is>
-          <t>547</t>
-        </is>
-      </c>
-      <c r="I41" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="J41" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="K41" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="L41" s="2" t="n">
-        <v>4.2</v>
-      </c>
-      <c r="M41" s="2" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="N41" s="2" t="n">
-        <v>3.4</v>
-      </c>
+      <c r="H41" s="2" t="inlineStr"/>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+      <c r="K41" s="2" t="inlineStr"/>
+      <c r="L41" s="2" t="inlineStr"/>
+      <c r="M41" s="2" t="inlineStr"/>
+      <c r="N41" s="2" t="inlineStr"/>
+      <c r="O41" s="2" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
         <is>
-          <t>HP Inc. - Taipei, TPQ</t>
+          <t>ASUS - Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="B42" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
+          <t>Hemel Hempstead, ENG</t>
         </is>
       </c>
       <c r="C42" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>United Kingdom</t>
         </is>
       </c>
       <c r="D42" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
-        </is>
-      </c>
-      <c r="E42" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F42" s="2" t="inlineStr">
-        <is>
-          <t>87%</t>
-        </is>
-      </c>
-      <c r="G42" s="2" t="inlineStr"/>
+          <t>Hemel Hempstead, ENG</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Hemel-Hempstead-Reviews-EI_IE40093.0,4_IL.5,20_IC2669775.htm</t>
+        </is>
+      </c>
+      <c r="F42" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="G42" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
       <c r="H42" s="2" t="inlineStr">
         <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="I42" s="2" t="n">
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="J42" s="2" t="n">
         <v>4.5</v>
-      </c>
-      <c r="J42" s="2" t="n">
-        <v>4.4</v>
       </c>
       <c r="K42" s="2" t="n">
         <v>3.8</v>
       </c>
       <c r="L42" s="2" t="n">
-        <v>4.4</v>
+        <v>2.8</v>
       </c>
       <c r="M42" s="2" t="n">
-        <v>3.7</v>
+        <v>4.3</v>
       </c>
       <c r="N42" s="2" t="n">
-        <v>3.6</v>
+        <v>3</v>
+      </c>
+      <c r="O42" s="2" t="n">
+        <v>3.8</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
         <is>
-          <t>Inventec - Global</t>
+          <t>ASUS - Milan, LOM</t>
         </is>
       </c>
       <c r="B43" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C43" s="2" t="inlineStr"/>
+          <t>Milan, LOM</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>Italy</t>
+        </is>
+      </c>
       <c r="D43" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E43" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F43" s="2" t="inlineStr">
-        <is>
-          <t>56%</t>
-        </is>
+          <t>Milan, LOM</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Milan-Reviews-EI_IE40093.0,4_IL.5,10_IC2802090.htm</t>
+        </is>
+      </c>
+      <c r="F43" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="G43" s="2" t="inlineStr">
         <is>
-          <t>77%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="H43" s="2" t="inlineStr">
         <is>
-          <t>162</t>
-        </is>
-      </c>
-      <c r="I43" s="2" t="n">
-        <v>3.6</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J43" s="2" t="n">
-        <v>3.5</v>
+        <v>3.3</v>
       </c>
       <c r="K43" s="2" t="n">
-        <v>3.1</v>
+        <v>2.4</v>
       </c>
       <c r="L43" s="2" t="n">
-        <v>3.2</v>
+        <v>1.5</v>
       </c>
       <c r="M43" s="2" t="n">
+        <v>2.4</v>
+      </c>
+      <c r="N43" s="2" t="n">
         <v>3.3</v>
       </c>
-      <c r="N43" s="2" t="n">
-        <v>3.1</v>
+      <c r="O43" s="2" t="n">
+        <v>3.3</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
         <is>
-          <t>Lenovo - Global</t>
+          <t>ASUS - Noisy-le-Grand, A8</t>
         </is>
       </c>
       <c r="B44" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C44" s="2" t="inlineStr"/>
+          <t>Noisy-le-Grand, A8</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
       <c r="D44" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E44" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F44" s="2" t="inlineStr">
-        <is>
-          <t>77%</t>
-        </is>
+          <t>Noisy-le-Grand, A8</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Noisy-le-Grand-Reviews-EI_IE40093.0,4_IL.5,19_IC3100822.htm</t>
+        </is>
+      </c>
+      <c r="F44" s="2" t="n">
+        <v>2.4</v>
       </c>
       <c r="G44" s="2" t="inlineStr">
         <is>
-          <t>87%</t>
+          <t>22%</t>
         </is>
       </c>
       <c r="H44" s="2" t="inlineStr">
         <is>
-          <t>3,519</t>
-        </is>
-      </c>
-      <c r="I44" s="2" t="n">
-        <v>4</v>
+          <t>23%</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
       </c>
       <c r="J44" s="2" t="n">
-        <v>3.7</v>
+        <v>2.8</v>
       </c>
       <c r="K44" s="2" t="n">
-        <v>3.8</v>
+        <v>2.2</v>
       </c>
       <c r="L44" s="2" t="n">
-        <v>3.8</v>
+        <v>2.1</v>
       </c>
       <c r="M44" s="2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="N44" s="2" t="n">
-        <v>3.4</v>
+        <v>2.1</v>
+      </c>
+      <c r="O44" s="2" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
         <is>
-          <t>Lenovo - Fremont, CA</t>
+          <t>ASUS - Ratingen, NW</t>
         </is>
       </c>
       <c r="B45" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
+          <t>Ratingen, NW</t>
         </is>
       </c>
       <c r="C45" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D45" s="2" t="inlineStr">
         <is>
-          <t>Chicago, IL</t>
-        </is>
-      </c>
-      <c r="E45" s="2" t="n">
-        <v>2</v>
-      </c>
-      <c r="F45" s="2" t="inlineStr">
-        <is>
-          <t>11%</t>
-        </is>
+          <t>Ratingen, NW</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Ratingen-Reviews-EI_IE40093.0,4_IL.5,13_IC2584004.htm</t>
+        </is>
+      </c>
+      <c r="F45" s="2" t="n">
+        <v>4</v>
       </c>
       <c r="G45" s="2" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>97%</t>
         </is>
       </c>
       <c r="H45" s="2" t="inlineStr">
         <is>
-          <t>45</t>
-        </is>
-      </c>
-      <c r="I45" s="2" t="n">
-        <v>2.2</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J45" s="2" t="n">
-        <v>1.3</v>
+        <v>1.4</v>
       </c>
       <c r="K45" s="2" t="n">
-        <v>2.7</v>
+        <v>3</v>
       </c>
       <c r="L45" s="2" t="n">
-        <v>1.7</v>
+        <v>1.6</v>
       </c>
       <c r="M45" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="N45" s="2" t="n">
         <v>2.3</v>
       </c>
-      <c r="N45" s="2" t="n">
-        <v>1.3</v>
+      <c r="O45" s="2" t="n">
+        <v>2.5</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
         <is>
-          <t>Lenovo - Ratingen, NW</t>
+          <t>ASUS - Bangkok, 10</t>
         </is>
       </c>
       <c r="B46" s="2" t="inlineStr">
         <is>
-          <t>Ratingen, NW</t>
+          <t>Bangkok, 10</t>
         </is>
       </c>
       <c r="C46" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Thailand</t>
         </is>
       </c>
       <c r="D46" s="2" t="inlineStr">
         <is>
-          <t>Stuttgart, BW</t>
-        </is>
-      </c>
-      <c r="E46" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F46" s="2" t="inlineStr">
-        <is>
-          <t>99%</t>
-        </is>
+          <t>Bangkok, 10</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Bangkok-Reviews-EI_IE40093.0,4_IL.5,12_IC3179725.htm</t>
+        </is>
+      </c>
+      <c r="F46" s="2" t="n">
+        <v>3.9</v>
       </c>
       <c r="G46" s="2" t="inlineStr">
         <is>
+          <t>79%</t>
+        </is>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="H46" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="I46" s="2" t="n">
-        <v>4.6</v>
+      <c r="I46" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="J46" s="2" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="K46" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="K46" s="2" t="n">
+      <c r="L46" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="L46" s="2" t="n">
-        <v>4.6</v>
-      </c>
       <c r="M46" s="2" t="n">
-        <v>3.4</v>
+        <v>3.7</v>
       </c>
       <c r="N46" s="2" t="n">
         <v>3.1</v>
       </c>
+      <c r="O46" s="2" t="n">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
         <is>
-          <t>Lenovo - Mumbai, MH</t>
+          <t>ASUS - Dubai, DU</t>
         </is>
       </c>
       <c r="B47" s="2" t="inlineStr">
         <is>
-          <t>Mumbai, MH</t>
+          <t>Dubai, DU</t>
         </is>
       </c>
       <c r="C47" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>United Arab Emirates</t>
         </is>
       </c>
       <c r="D47" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, KA</t>
-        </is>
-      </c>
-      <c r="E47" s="2" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="F47" s="2" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
+          <t>Dubai, DU</t>
+        </is>
+      </c>
+      <c r="E47" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Dubai-Reviews-EI_IE40093.0,4_IL.5,10_IC2204498.htm</t>
+        </is>
+      </c>
+      <c r="F47" s="2" t="n">
+        <v>2.6</v>
       </c>
       <c r="G47" s="2" t="inlineStr">
         <is>
-          <t>94%</t>
+          <t>3%</t>
         </is>
       </c>
       <c r="H47" s="2" t="inlineStr">
         <is>
-          <t>192</t>
-        </is>
-      </c>
-      <c r="I47" s="2" t="n">
-        <v>3.8</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="inlineStr">
+        <is>
+          <t>19</t>
+        </is>
       </c>
       <c r="J47" s="2" t="n">
-        <v>3.5</v>
+        <v>2.3</v>
       </c>
       <c r="K47" s="2" t="n">
-        <v>3.9</v>
+        <v>1.9</v>
       </c>
       <c r="L47" s="2" t="n">
-        <v>3.7</v>
+        <v>1.7</v>
       </c>
       <c r="M47" s="2" t="n">
-        <v>3.2</v>
+        <v>2.2</v>
       </c>
       <c r="N47" s="2" t="n">
-        <v>3.1</v>
+        <v>2.3</v>
+      </c>
+      <c r="O47" s="2" t="n">
+        <v>2.2</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
         <is>
-          <t>Lenovo - São Paulo, SP</t>
+          <t>ASUS - Jakarta, JK</t>
         </is>
       </c>
       <c r="B48" s="2" t="inlineStr">
         <is>
-          <t>São Paulo, SP</t>
+          <t>Jakarta, JK</t>
         </is>
       </c>
       <c r="C48" s="2" t="inlineStr">
         <is>
-          <t>Brazil</t>
+          <t>Indonesia</t>
         </is>
       </c>
       <c r="D48" s="2" t="inlineStr">
         <is>
-          <t>Campinas, SP</t>
-        </is>
-      </c>
-      <c r="E48" s="2" t="inlineStr"/>
-      <c r="F48" s="2" t="inlineStr"/>
-      <c r="G48" s="2" t="inlineStr"/>
-      <c r="H48" s="2" t="inlineStr"/>
-      <c r="I48" s="2" t="inlineStr"/>
-      <c r="J48" s="2" t="inlineStr"/>
-      <c r="K48" s="2" t="inlineStr"/>
-      <c r="L48" s="2" t="inlineStr"/>
-      <c r="M48" s="2" t="inlineStr"/>
-      <c r="N48" s="2" t="inlineStr"/>
+          <t>Jakarta, JK</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Jakarta-Reviews-EI_IE40093.0,4_IL.5,12_IC2709872.htm</t>
+        </is>
+      </c>
+      <c r="F48" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G48" s="2" t="inlineStr">
+        <is>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J48" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K48" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="L48" s="2" t="n">
+        <v>4.3</v>
+      </c>
+      <c r="M48" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="N48" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="O48" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
         <is>
-          <t>Lenovo - Sydney, NSW</t>
+          <t>ASUS - Kuala Lumpur, 14</t>
         </is>
       </c>
       <c r="B49" s="2" t="inlineStr">
         <is>
-          <t>Sydney, NSW</t>
+          <t>Kuala Lumpur, 14</t>
         </is>
       </c>
       <c r="C49" s="2" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Malaysia</t>
         </is>
       </c>
       <c r="D49" s="2" t="inlineStr">
         <is>
-          <t>Sydney, NSW</t>
-        </is>
-      </c>
-      <c r="E49" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F49" s="2" t="inlineStr">
-        <is>
-          <t>53%</t>
-        </is>
+          <t>Kuala Lumpur, 14</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Kuala-Lumpur-Reviews-EI_IE40093.0,4_IL.5,17_IC2986682.htm</t>
+        </is>
+      </c>
+      <c r="F49" s="2" t="n">
+        <v>4.9</v>
       </c>
       <c r="G49" s="2" t="inlineStr">
         <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="H49" s="2" t="inlineStr">
-        <is>
-          <t>42</t>
-        </is>
-      </c>
-      <c r="I49" s="2" t="n">
-        <v>2.9</v>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="H49" s="2" t="inlineStr"/>
+      <c r="I49" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="J49" s="2" t="n">
-        <v>2.3</v>
+        <v>4</v>
       </c>
       <c r="K49" s="2" t="n">
-        <v>2.8</v>
+        <v>4</v>
       </c>
       <c r="L49" s="2" t="n">
-        <v>2.5</v>
+        <v>4.9</v>
       </c>
       <c r="M49" s="2" t="n">
-        <v>2.5</v>
+        <v>4</v>
       </c>
       <c r="N49" s="2" t="n">
-        <v>2.6</v>
+        <v>5</v>
+      </c>
+      <c r="O49" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
         <is>
-          <t>MSI - Global</t>
+          <t>ASUS - Manila, D9</t>
         </is>
       </c>
       <c r="B50" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C50" s="2" t="inlineStr"/>
+          <t>Manila, D9</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
       <c r="D50" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E50" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F50" s="2" t="inlineStr">
-        <is>
-          <t>75%</t>
-        </is>
+          <t>Manila, D9</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Manila-Reviews-EI_IE40093.0,4_IL.5,11_IC2363570.htm</t>
+        </is>
+      </c>
+      <c r="F50" s="2" t="n">
+        <v>4.1</v>
       </c>
       <c r="G50" s="2" t="inlineStr">
         <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="H50" s="2" t="inlineStr">
-        <is>
-          <t>63</t>
-        </is>
-      </c>
-      <c r="I50" s="2" t="n">
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="H50" s="2" t="inlineStr"/>
+      <c r="I50" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="J50" s="2" t="n">
         <v>3.9</v>
       </c>
-      <c r="J50" s="2" t="n">
-        <v>3.8</v>
-      </c>
       <c r="K50" s="2" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="L50" s="2" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="M50" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="N50" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="L50" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="M50" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N50" s="2" t="n">
-        <v>3.4</v>
+      <c r="O50" s="2" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Global</t>
+          <t>ASUS - Mumbai, MH</t>
         </is>
       </c>
       <c r="B51" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C51" s="2" t="inlineStr"/>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>India</t>
+        </is>
+      </c>
       <c r="D51" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E51" s="2" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="F51" s="2" t="inlineStr">
-        <is>
-          <t>90%</t>
-        </is>
+          <t>Mumbai, MH</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Mumbai-Reviews-EI_IE40093.0,4_IL.5,11_IC2851180.htm</t>
+        </is>
+      </c>
+      <c r="F51" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="G51" s="2" t="inlineStr">
         <is>
-          <t>97%</t>
+          <t>99%</t>
         </is>
       </c>
       <c r="H51" s="2" t="inlineStr">
         <is>
-          <t>5,442</t>
-        </is>
-      </c>
-      <c r="I51" s="2" t="n">
-        <v>4.4</v>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="inlineStr">
+        <is>
+          <t>28</t>
+        </is>
       </c>
       <c r="J51" s="2" t="n">
-        <v>3.9</v>
+        <v>3.4</v>
       </c>
       <c r="K51" s="2" t="n">
-        <v>4.4</v>
+        <v>3.7</v>
       </c>
       <c r="L51" s="2" t="n">
-        <v>4.3</v>
+        <v>3</v>
       </c>
       <c r="M51" s="2" t="n">
-        <v>4.3</v>
+        <v>3.1</v>
       </c>
       <c r="N51" s="2" t="n">
-        <v>4.2</v>
+        <v>3.4</v>
+      </c>
+      <c r="O51" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Fremont, CA</t>
+          <t>ASUS - Seoul, 11</t>
         </is>
       </c>
       <c r="B52" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
+          <t>Seoul, 11</t>
         </is>
       </c>
       <c r="C52" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>South Korea</t>
         </is>
       </c>
       <c r="D52" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="E52" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F52" s="2" t="inlineStr">
-        <is>
-          <t>91%</t>
-        </is>
+          <t>Seoul, 11</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Seoul-Reviews-EI_IE40093.0,4_IL.5,10_IC3021489.htm</t>
+        </is>
+      </c>
+      <c r="F52" s="2" t="n">
+        <v>3</v>
       </c>
       <c r="G52" s="2" t="inlineStr">
         <is>
-          <t>91%</t>
-        </is>
-      </c>
-      <c r="H52" s="2" t="inlineStr">
-        <is>
-          <t>78</t>
-        </is>
-      </c>
-      <c r="I52" s="2" t="n">
-        <v>4.2</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="H52" s="2" t="inlineStr"/>
+      <c r="I52" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J52" s="2" t="n">
-        <v>4.4</v>
+        <v>3</v>
       </c>
       <c r="K52" s="2" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="L52" s="2" t="n">
-        <v>4.3</v>
+        <v>2</v>
       </c>
       <c r="M52" s="2" t="n">
-        <v>4.5</v>
+        <v>3</v>
       </c>
       <c r="N52" s="2" t="n">
-        <v>4.6</v>
+        <v>4</v>
+      </c>
+      <c r="O52" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Markham, ON</t>
+          <t>ASUS - Singapore</t>
         </is>
       </c>
       <c r="B53" s="2" t="inlineStr">
         <is>
-          <t>Markham, ON</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="C53" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>Singapore</t>
         </is>
       </c>
       <c r="D53" s="2" t="inlineStr">
         <is>
-          <t>Toronto, ON</t>
-        </is>
-      </c>
-      <c r="E53" s="2" t="n">
-        <v>4.9</v>
-      </c>
-      <c r="F53" s="2" t="inlineStr">
-        <is>
-          <t>88%</t>
-        </is>
+          <t>Singapore</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Singapore-Reviews-EI_IE40093.0,4_IL.5,14_IC3235921.htm</t>
+        </is>
+      </c>
+      <c r="F53" s="2" t="n">
+        <v>2.8</v>
       </c>
       <c r="G53" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>37%</t>
         </is>
       </c>
       <c r="H53" s="2" t="inlineStr">
         <is>
-          <t>23</t>
-        </is>
-      </c>
-      <c r="I53" s="2" t="n">
-        <v>4.8</v>
+          <t>44%</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="J53" s="2" t="n">
-        <v>4.5</v>
+        <v>3.1</v>
       </c>
       <c r="K53" s="2" t="n">
-        <v>5</v>
+        <v>2.7</v>
       </c>
       <c r="L53" s="2" t="n">
-        <v>4.8</v>
+        <v>2.7</v>
       </c>
       <c r="M53" s="2" t="n">
-        <v>4.6</v>
+        <v>2.6</v>
       </c>
       <c r="N53" s="2" t="n">
-        <v>4.8</v>
+        <v>2.6</v>
+      </c>
+      <c r="O53" s="2" t="n">
+        <v>2.3</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Hemel Hempstead, ENG</t>
+          <t>ASUS - Taipei, TPQ</t>
         </is>
       </c>
       <c r="B54" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead, ENG</t>
+          <t>Taipei, TPQ</t>
         </is>
       </c>
       <c r="C54" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D54" s="2" t="inlineStr">
         <is>
-          <t>Reading, ENG</t>
-        </is>
-      </c>
-      <c r="E54" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F54" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E54" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Taipei-Reviews-EI_IE40093.0,4_IL.5,11_IC3271041.htm</t>
+        </is>
+      </c>
+      <c r="F54" s="2" t="n">
+        <v>3.7</v>
       </c>
       <c r="G54" s="2" t="inlineStr">
         <is>
-          <t>93%</t>
+          <t>67%</t>
         </is>
       </c>
       <c r="H54" s="2" t="inlineStr">
         <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="I54" s="2" t="n">
-        <v>5</v>
+          <t>98%</t>
+        </is>
+      </c>
+      <c r="I54" s="2" t="inlineStr">
+        <is>
+          <t>524</t>
+        </is>
       </c>
       <c r="J54" s="2" t="n">
-        <v>4</v>
+        <v>3.3</v>
       </c>
       <c r="K54" s="2" t="n">
-        <v>5</v>
+        <v>3.8</v>
       </c>
       <c r="L54" s="2" t="n">
-        <v>5</v>
+        <v>3.3</v>
       </c>
       <c r="M54" s="2" t="n">
-        <v>5</v>
+        <v>3.1</v>
       </c>
       <c r="N54" s="2" t="n">
-        <v>4.4</v>
+        <v>3.5</v>
+      </c>
+      <c r="O54" s="2" t="n">
+        <v>2.8</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Ratingen, NW</t>
+          <t>ASUS - Tokyo, 40</t>
         </is>
       </c>
       <c r="B55" s="2" t="inlineStr">
         <is>
-          <t>Ratingen, NW</t>
+          <t>Tokyo, 40</t>
         </is>
       </c>
       <c r="C55" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>Japan</t>
         </is>
       </c>
       <c r="D55" s="2" t="inlineStr">
         <is>
-          <t>Munich, BY</t>
-        </is>
-      </c>
-      <c r="E55" s="2" t="n">
-        <v>5</v>
-      </c>
-      <c r="F55" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="G55" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H55" s="2" t="inlineStr">
-        <is>
-          <t>19</t>
-        </is>
-      </c>
-      <c r="I55" s="2" t="n">
-        <v>4.8</v>
+          <t>Tokyo, 40</t>
+        </is>
+      </c>
+      <c r="E55" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Tokyo-Reviews-EI_IE40093.0,4_IL.5,10_IC2851580.htm</t>
+        </is>
+      </c>
+      <c r="F55" s="2" t="n">
+        <v>1</v>
+      </c>
+      <c r="G55" s="2" t="inlineStr"/>
+      <c r="H55" s="2" t="inlineStr"/>
+      <c r="I55" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="J55" s="2" t="n">
-        <v>3.9</v>
+        <v>1</v>
       </c>
       <c r="K55" s="2" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L55" s="2" t="n">
-        <v>4.9</v>
+        <v>2</v>
       </c>
       <c r="M55" s="2" t="n">
-        <v>4.6</v>
+        <v>1</v>
       </c>
       <c r="N55" s="2" t="n">
-        <v>4.9</v>
+        <v>1</v>
+      </c>
+      <c r="O55" s="2" t="n">
+        <v>3</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Mumbai, MH</t>
+          <t>ASUS - Santiago, RM</t>
         </is>
       </c>
       <c r="B56" s="2" t="inlineStr">
         <is>
-          <t>Mumbai, MH</t>
+          <t>Santiago, RM</t>
         </is>
       </c>
       <c r="C56" s="2" t="inlineStr">
         <is>
-          <t>India</t>
+          <t>Chile</t>
         </is>
       </c>
       <c r="D56" s="2" t="inlineStr">
         <is>
-          <t>Bengaluru, KA</t>
-        </is>
-      </c>
-      <c r="E56" s="2" t="inlineStr"/>
-      <c r="F56" s="2" t="inlineStr"/>
-      <c r="G56" s="2" t="inlineStr"/>
+          <t>Santiago, RM</t>
+        </is>
+      </c>
+      <c r="E56" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Santiago-Reviews-EI_IE40093.0,4_IL.5,13_IC2434030.htm</t>
+        </is>
+      </c>
+      <c r="F56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="G56" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
       <c r="H56" s="2" t="inlineStr"/>
-      <c r="I56" s="2" t="inlineStr"/>
-      <c r="J56" s="2" t="inlineStr"/>
-      <c r="K56" s="2" t="inlineStr"/>
-      <c r="L56" s="2" t="inlineStr"/>
-      <c r="M56" s="2" t="inlineStr"/>
-      <c r="N56" s="2" t="inlineStr"/>
+      <c r="I56" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="K56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="L56" s="2" t="n">
+        <v>3</v>
+      </c>
+      <c r="M56" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="N56" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="O56" s="2" t="n">
+        <v>4</v>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
         <is>
-          <t>NVIDIA - Taipei, TPQ</t>
+          <t>ASUS - São Paulo, SP</t>
         </is>
       </c>
       <c r="B57" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
+          <t>São Paulo, SP</t>
         </is>
       </c>
       <c r="C57" s="2" t="inlineStr">
         <is>
-          <t>Taiwan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D57" s="2" t="inlineStr">
         <is>
-          <t>Hsinchu, TXG</t>
-        </is>
-      </c>
-      <c r="E57" s="2" t="n">
-        <v>4.6</v>
-      </c>
-      <c r="F57" s="2" t="inlineStr">
+          <t>São Paulo, SP</t>
+        </is>
+      </c>
+      <c r="E57" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-S%C3%A3o-Paulo-Reviews-EI_IE40093.0,4_IL.5,14_IC2479061.htm</t>
+        </is>
+      </c>
+      <c r="F57" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="G57" s="2" t="inlineStr">
+        <is>
+          <t>55%</t>
+        </is>
+      </c>
+      <c r="H57" s="2" t="inlineStr">
         <is>
           <t>100%</t>
         </is>
       </c>
-      <c r="G57" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
-      </c>
-      <c r="H57" s="2" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="I57" s="2" t="n">
-        <v>4</v>
+      <c r="I57" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
       </c>
       <c r="J57" s="2" t="n">
-        <v>4</v>
+        <v>3.1</v>
       </c>
       <c r="K57" s="2" t="n">
-        <v>4.4</v>
+        <v>2.4</v>
       </c>
       <c r="L57" s="2" t="n">
-        <v>5</v>
+        <v>3.7</v>
       </c>
       <c r="M57" s="2" t="n">
-        <v>4.4</v>
+        <v>2.3</v>
       </c>
       <c r="N57" s="2" t="n">
-        <v>3.7</v>
+        <v>1.6</v>
+      </c>
+      <c r="O57" s="2" t="n">
+        <v>2.1</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
         <is>
-          <t>Pegatron - Global</t>
+          <t>ASUS - Sydney, NSW</t>
         </is>
       </c>
       <c r="B58" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C58" s="2" t="inlineStr"/>
+          <t>Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="C58" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
       <c r="D58" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E58" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F58" s="2" t="inlineStr">
-        <is>
-          <t>44%</t>
-        </is>
+          <t>Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="E58" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/ASUS-Sydney-Reviews-EI_IE40093.0,4_IL.5,11_IC2235932.htm</t>
+        </is>
+      </c>
+      <c r="F58" s="2" t="n">
+        <v>1.2</v>
       </c>
       <c r="G58" s="2" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>1%</t>
         </is>
       </c>
       <c r="H58" s="2" t="inlineStr">
         <is>
-          <t>506</t>
-        </is>
-      </c>
-      <c r="I58" s="2" t="n">
-        <v>3.3</v>
+          <t>53%</t>
+        </is>
+      </c>
+      <c r="I58" s="2" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
       </c>
       <c r="J58" s="2" t="n">
-        <v>3.2</v>
+        <v>1</v>
       </c>
       <c r="K58" s="2" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="L58" s="2" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="M58" s="2" t="n">
-        <v>3.1</v>
+        <v>1</v>
       </c>
       <c r="N58" s="2" t="n">
-        <v>2.9</v>
+        <v>1</v>
+      </c>
+      <c r="O58" s="2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
         <is>
-          <t>Pegatron - Fremont, CA</t>
+          <t>Compal Electronics - Global</t>
         </is>
       </c>
       <c r="B59" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
-        </is>
-      </c>
-      <c r="C59" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C59" s="2" t="inlineStr"/>
       <c r="D59" s="2" t="inlineStr">
         <is>
-          <t>Jeffersonville, IN</t>
-        </is>
-      </c>
-      <c r="E59" s="2" t="inlineStr"/>
-      <c r="F59" s="2" t="inlineStr"/>
-      <c r="G59" s="2" t="inlineStr"/>
-      <c r="H59" s="2" t="inlineStr"/>
-      <c r="I59" s="2" t="inlineStr"/>
-      <c r="J59" s="2" t="inlineStr"/>
-      <c r="K59" s="2" t="inlineStr"/>
-      <c r="L59" s="2" t="inlineStr"/>
-      <c r="M59" s="2" t="inlineStr"/>
-      <c r="N59" s="2" t="inlineStr"/>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E59" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Delta-Electronics-Reviews-E41146.htm</t>
+        </is>
+      </c>
+      <c r="F59" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="G59" s="2" t="inlineStr">
+        <is>
+          <t>66%</t>
+        </is>
+      </c>
+      <c r="H59" s="2" t="inlineStr">
+        <is>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="I59" s="2" t="inlineStr">
+        <is>
+          <t>754</t>
+        </is>
+      </c>
+      <c r="J59" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K59" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L59" s="2" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="M59" s="2" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="N59" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="O59" s="2" t="n">
+        <v>3.2</v>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
         <is>
-          <t>Quanta Computer - Global</t>
+          <t>Compal Electronics - Emmen, DR</t>
         </is>
       </c>
       <c r="B60" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C60" s="2" t="inlineStr"/>
+          <t>Emmen, DR</t>
+        </is>
+      </c>
+      <c r="C60" s="2" t="inlineStr">
+        <is>
+          <t>Netherlands</t>
+        </is>
+      </c>
       <c r="D60" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E60" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="F60" s="2" t="inlineStr">
-        <is>
-          <t>50%</t>
-        </is>
+          <t>Hoofddorp, NH</t>
+        </is>
+      </c>
+      <c r="E60" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Delta-Electronics-Hoofddorp-Reviews-EI_IE41146.0,17_IL.18,27_IC3063772.htm</t>
+        </is>
+      </c>
+      <c r="F60" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="G60" s="2" t="inlineStr">
         <is>
-          <t>54%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="H60" s="2" t="inlineStr">
         <is>
-          <t>570</t>
-        </is>
-      </c>
-      <c r="I60" s="2" t="n">
-        <v>3.2</v>
+          <t>99%</t>
+        </is>
+      </c>
+      <c r="I60" s="2" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
       </c>
       <c r="J60" s="2" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="K60" s="2" t="n">
-        <v>3</v>
+        <v>3.3</v>
       </c>
       <c r="L60" s="2" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="M60" s="2" t="n">
         <v>3.1</v>
       </c>
       <c r="N60" s="2" t="n">
-        <v>2.7</v>
+        <v>2.3</v>
+      </c>
+      <c r="O60" s="2" t="n">
+        <v>2.6</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
         <is>
-          <t>Quanta Computer - Fremont, CA</t>
+          <t>Compal Electronics - Taipei, TPQ</t>
         </is>
       </c>
       <c r="B61" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
+          <t>Taipei, TPQ</t>
         </is>
       </c>
       <c r="C61" s="2" t="inlineStr">
         <is>
-          <t>United States</t>
+          <t>Taiwan</t>
         </is>
       </c>
       <c r="D61" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
-        </is>
-      </c>
-      <c r="E61" s="2" t="inlineStr"/>
-      <c r="F61" s="2" t="inlineStr"/>
-      <c r="G61" s="2" t="inlineStr"/>
-      <c r="H61" s="2" t="inlineStr"/>
-      <c r="I61" s="2" t="inlineStr"/>
-      <c r="J61" s="2" t="inlineStr"/>
-      <c r="K61" s="2" t="inlineStr"/>
-      <c r="L61" s="2" t="inlineStr"/>
-      <c r="M61" s="2" t="inlineStr"/>
-      <c r="N61" s="2" t="inlineStr"/>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="E61" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Delta-Electronics-Taipei-Reviews-EI_IE41146.0,17_IL.18,24_IC3271041.htm</t>
+        </is>
+      </c>
+      <c r="F61" s="2" t="n">
+        <v>4</v>
+      </c>
+      <c r="G61" s="2" t="inlineStr">
+        <is>
+          <t>93%</t>
+        </is>
+      </c>
+      <c r="H61" s="2" t="inlineStr">
+        <is>
+          <t>90%</t>
+        </is>
+      </c>
+      <c r="I61" s="2" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="J61" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="K61" s="2" t="n">
+        <v>4.2</v>
+      </c>
+      <c r="L61" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="M61" s="2" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="N61" s="2" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="O61" s="2" t="n">
+        <v>3.4</v>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
         <is>
-          <t>Trend Micro - Global</t>
+          <t>Google - Global</t>
         </is>
       </c>
       <c r="B62" s="2" t="inlineStr">
@@ -3735,187 +4153,198 @@
           <t>Global</t>
         </is>
       </c>
-      <c r="E62" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="F62" s="2" t="inlineStr">
-        <is>
-          <t>71%</t>
-        </is>
+      <c r="E62" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Google-Reviews-E9079.htm</t>
+        </is>
+      </c>
+      <c r="F62" s="2" t="n">
+        <v>4.4</v>
       </c>
       <c r="G62" s="2" t="inlineStr">
         <is>
-          <t>75%</t>
+          <t>87%</t>
         </is>
       </c>
       <c r="H62" s="2" t="inlineStr">
         <is>
-          <t>2,073</t>
-        </is>
-      </c>
-      <c r="I62" s="2" t="n">
-        <v>4</v>
+          <t>82%</t>
+        </is>
+      </c>
+      <c r="I62" s="2" t="inlineStr">
+        <is>
+          <t>48,118</t>
+        </is>
       </c>
       <c r="J62" s="2" t="n">
-        <v>4</v>
+        <v>4.4</v>
       </c>
       <c r="K62" s="2" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
       </c>
       <c r="L62" s="2" t="n">
-        <v>4</v>
+        <v>4.5</v>
       </c>
       <c r="M62" s="2" t="n">
-        <v>3.6</v>
+        <v>4.2</v>
       </c>
       <c r="N62" s="2" t="n">
-        <v>3.3</v>
+        <v>4.2</v>
+      </c>
+      <c r="O62" s="2" t="n">
+        <v>3.9</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
         <is>
-          <t>Trend Micro - Fremont, CA</t>
+          <t>Lenovo - Global</t>
         </is>
       </c>
       <c r="B63" s="2" t="inlineStr">
         <is>
-          <t>Fremont, CA</t>
-        </is>
-      </c>
-      <c r="C63" s="2" t="inlineStr">
-        <is>
-          <t>United States</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C63" s="2" t="inlineStr"/>
       <c r="D63" s="2" t="inlineStr">
         <is>
-          <t>Austin, TX</t>
-        </is>
-      </c>
-      <c r="E63" s="2" t="n">
-        <v>4.3</v>
-      </c>
-      <c r="F63" s="2" t="inlineStr">
-        <is>
-          <t>72%</t>
-        </is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E63" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Lenovo-Reviews-E8034.htm</t>
+        </is>
+      </c>
+      <c r="F63" s="2" t="n">
+        <v>3.9</v>
       </c>
       <c r="G63" s="2" t="inlineStr">
         <is>
-          <t>68%</t>
+          <t>77%</t>
         </is>
       </c>
       <c r="H63" s="2" t="inlineStr">
         <is>
-          <t>36</t>
-        </is>
-      </c>
-      <c r="I63" s="2" t="n">
-        <v>4.2</v>
+          <t>87%</t>
+        </is>
+      </c>
+      <c r="I63" s="2" t="inlineStr">
+        <is>
+          <t>3,519</t>
+        </is>
       </c>
       <c r="J63" s="2" t="n">
-        <v>4.7</v>
+        <v>4</v>
       </c>
       <c r="K63" s="2" t="n">
-        <v>3.2</v>
+        <v>3.7</v>
       </c>
       <c r="L63" s="2" t="n">
-        <v>4.2</v>
+        <v>3.8</v>
       </c>
       <c r="M63" s="2" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="N63" s="2" t="n">
-        <v>3.1</v>
+        <v>3.5</v>
+      </c>
+      <c r="O63" s="2" t="n">
+        <v>3.4</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
         <is>
-          <t>Trend Micro - Markham, ON</t>
+          <t>Lenovo - Fremont, CA</t>
         </is>
       </c>
       <c r="B64" s="2" t="inlineStr">
         <is>
-          <t>Markham, ON</t>
+          <t>Fremont, CA</t>
         </is>
       </c>
       <c r="C64" s="2" t="inlineStr">
         <is>
-          <t>Canada</t>
+          <t>United States</t>
         </is>
       </c>
       <c r="D64" s="2" t="inlineStr">
         <is>
-          <t>Kanata, ON</t>
-        </is>
-      </c>
-      <c r="E64" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F64" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
+          <t>Chicago, IL</t>
+        </is>
+      </c>
+      <c r="E64" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Lenovo-Chicago-Reviews-EI_IE8034.0,6_IL.7,14_IC1128808.htm</t>
+        </is>
+      </c>
+      <c r="F64" s="2" t="n">
+        <v>2</v>
       </c>
       <c r="G64" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>11%</t>
         </is>
       </c>
       <c r="H64" s="2" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="I64" s="2" t="n">
-        <v>4</v>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="I64" s="2" t="inlineStr">
+        <is>
+          <t>45</t>
+        </is>
       </c>
       <c r="J64" s="2" t="n">
-        <v>5</v>
+        <v>2.2</v>
       </c>
       <c r="K64" s="2" t="n">
-        <v>3</v>
+        <v>1.3</v>
       </c>
       <c r="L64" s="2" t="n">
-        <v>4</v>
+        <v>2.7</v>
       </c>
       <c r="M64" s="2" t="n">
-        <v>4</v>
+        <v>1.7</v>
       </c>
       <c r="N64" s="2" t="n">
-        <v>3</v>
+        <v>2.3</v>
+      </c>
+      <c r="O64" s="2" t="n">
+        <v>1.3</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
         <is>
-          <t>Trend Micro - Hemel Hempstead, ENG</t>
+          <t>Lenovo - Ratingen, NW</t>
         </is>
       </c>
       <c r="B65" s="2" t="inlineStr">
         <is>
-          <t>Hemel Hempstead, ENG</t>
+          <t>Ratingen, NW</t>
         </is>
       </c>
       <c r="C65" s="2" t="inlineStr">
         <is>
-          <t>United Kingdom</t>
+          <t>Germany</t>
         </is>
       </c>
       <c r="D65" s="2" t="inlineStr">
         <is>
-          <t>London, ENG</t>
-        </is>
-      </c>
-      <c r="E65" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F65" s="2" t="inlineStr">
-        <is>
-          <t>85%</t>
-        </is>
+          <t>Stuttgart, BW</t>
+        </is>
+      </c>
+      <c r="E65" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Lenovo-Stuttgart-Reviews-EI_IE8034.0,6_IL.7,16_IC2507190.htm</t>
+        </is>
+      </c>
+      <c r="F65" s="2" t="n">
+        <v>5</v>
       </c>
       <c r="G65" s="2" t="inlineStr">
         <is>
@@ -3924,389 +4353,463 @@
       </c>
       <c r="H65" s="2" t="inlineStr">
         <is>
-          <t>28</t>
-        </is>
-      </c>
-      <c r="I65" s="2" t="n">
-        <v>3.2</v>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I65" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="J65" s="2" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="K65" s="2" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="L65" s="2" t="n">
         <v>4</v>
       </c>
-      <c r="K65" s="2" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="L65" s="2" t="n">
-        <v>3.6</v>
-      </c>
       <c r="M65" s="2" t="n">
-        <v>3.3</v>
+        <v>4.6</v>
       </c>
       <c r="N65" s="2" t="n">
-        <v>2.9</v>
+        <v>3.4</v>
+      </c>
+      <c r="O65" s="2" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
         <is>
-          <t>Trend Micro - Ratingen, NW</t>
+          <t>Lenovo - Mumbai, MH</t>
         </is>
       </c>
       <c r="B66" s="2" t="inlineStr">
         <is>
-          <t>Ratingen, NW</t>
+          <t>Mumbai, MH</t>
         </is>
       </c>
       <c r="C66" s="2" t="inlineStr">
         <is>
-          <t>Germany</t>
+          <t>India</t>
         </is>
       </c>
       <c r="D66" s="2" t="inlineStr">
         <is>
-          <t>Munich, BY</t>
-        </is>
-      </c>
-      <c r="E66" s="2" t="n">
-        <v>4</v>
-      </c>
-      <c r="F66" s="2" t="inlineStr">
-        <is>
-          <t>100%</t>
-        </is>
+          <t>Bengaluru, KA</t>
+        </is>
+      </c>
+      <c r="E66" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Lenovo-Bengaluru-Reviews-EI_IE8034.0,6_IL.7,16_IC2940587.htm</t>
+        </is>
+      </c>
+      <c r="F66" s="2" t="n">
+        <v>3.9</v>
       </c>
       <c r="G66" s="2" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>71%</t>
         </is>
       </c>
       <c r="H66" s="2" t="inlineStr">
         <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="I66" s="2" t="n">
-        <v>4.4</v>
+          <t>94%</t>
+        </is>
+      </c>
+      <c r="I66" s="2" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
       </c>
       <c r="J66" s="2" t="n">
-        <v>4</v>
+        <v>3.8</v>
       </c>
       <c r="K66" s="2" t="n">
-        <v>4</v>
+        <v>3.5</v>
       </c>
       <c r="L66" s="2" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="M66" s="2" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="N66" s="2" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
+      </c>
+      <c r="O66" s="2" t="n">
+        <v>3.1</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
         <is>
-          <t>Trend Micro - Tokyo, 40</t>
+          <t>Lenovo - São Paulo, SP</t>
         </is>
       </c>
       <c r="B67" s="2" t="inlineStr">
         <is>
-          <t>Tokyo, 40</t>
+          <t>São Paulo, SP</t>
         </is>
       </c>
       <c r="C67" s="2" t="inlineStr">
         <is>
-          <t>Japan</t>
+          <t>Brazil</t>
         </is>
       </c>
       <c r="D67" s="2" t="inlineStr">
         <is>
-          <t>Tokyo, 40</t>
-        </is>
-      </c>
-      <c r="E67" s="2" t="inlineStr"/>
-      <c r="F67" s="2" t="inlineStr"/>
-      <c r="G67" s="2" t="inlineStr"/>
-      <c r="H67" s="2" t="inlineStr"/>
-      <c r="I67" s="2" t="inlineStr"/>
-      <c r="J67" s="2" t="inlineStr"/>
-      <c r="K67" s="2" t="inlineStr"/>
-      <c r="L67" s="2" t="inlineStr"/>
-      <c r="M67" s="2" t="inlineStr"/>
-      <c r="N67" s="2" t="inlineStr"/>
+          <t>Campinas, SP</t>
+        </is>
+      </c>
+      <c r="E67" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Lenovo-Campinas-Reviews-EI_IE8034.0,6_IL.7,15_IC2490130.htm</t>
+        </is>
+      </c>
+      <c r="F67" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="G67" s="2" t="inlineStr">
+        <is>
+          <t>36%</t>
+        </is>
+      </c>
+      <c r="H67" s="2" t="inlineStr">
+        <is>
+          <t>100%</t>
+        </is>
+      </c>
+      <c r="I67" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J67" s="2" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="K67" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="L67" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="M67" s="2" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="N67" s="2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="O67" s="2" t="n">
+        <v>1.9</v>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
         <is>
-          <t>TSMC - Global</t>
+          <t>Lenovo - Sydney, NSW</t>
         </is>
       </c>
       <c r="B68" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C68" s="2" t="inlineStr"/>
+          <t>Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="C68" s="2" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
       <c r="D68" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E68" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="F68" s="2" t="inlineStr">
-        <is>
-          <t>46%</t>
-        </is>
+          <t>Sydney, NSW</t>
+        </is>
+      </c>
+      <c r="E68" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Lenovo-Sydney-Reviews-EI_IE8034.0,6_IL.7,13_IC2235932.htm</t>
+        </is>
+      </c>
+      <c r="F68" s="2" t="n">
+        <v>3.5</v>
       </c>
       <c r="G68" s="2" t="inlineStr">
         <is>
-          <t>74%</t>
+          <t>53%</t>
         </is>
       </c>
       <c r="H68" s="2" t="inlineStr">
         <is>
-          <t>2,135</t>
-        </is>
-      </c>
-      <c r="I68" s="2" t="n">
+          <t>59%</t>
+        </is>
+      </c>
+      <c r="I68" s="2" t="inlineStr">
+        <is>
+          <t>42</t>
+        </is>
+      </c>
+      <c r="J68" s="2" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="K68" s="2" t="n">
+        <v>2.3</v>
+      </c>
+      <c r="L68" s="2" t="n">
         <v>2.8</v>
       </c>
-      <c r="J68" s="2" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="K68" s="2" t="n">
-        <v>3.8</v>
-      </c>
-      <c r="L68" s="2" t="n">
+      <c r="M68" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="N68" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="O68" s="2" t="n">
         <v>2.6</v>
-      </c>
-      <c r="M68" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N68" s="2" t="n">
-        <v>2.7</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
         <is>
-          <t>TSMC - Taipei, TPQ</t>
+          <t>Pegatron - Global</t>
         </is>
       </c>
       <c r="B69" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
-        </is>
-      </c>
-      <c r="C69" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C69" s="2" t="inlineStr"/>
       <c r="D69" s="2" t="inlineStr">
         <is>
-          <t>Hsinchu, TXG</t>
-        </is>
-      </c>
-      <c r="E69" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="F69" s="2" t="inlineStr">
-        <is>
-          <t>52%</t>
-        </is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E69" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Pegatron-Reviews-E337948.htm</t>
+        </is>
+      </c>
+      <c r="F69" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="G69" s="2" t="inlineStr">
         <is>
-          <t>81%</t>
+          <t>44%</t>
         </is>
       </c>
       <c r="H69" s="2" t="inlineStr">
         <is>
-          <t>613</t>
-        </is>
-      </c>
-      <c r="I69" s="2" t="n">
-        <v>2.9</v>
+          <t>69%</t>
+        </is>
+      </c>
+      <c r="I69" s="2" t="inlineStr">
+        <is>
+          <t>506</t>
+        </is>
       </c>
       <c r="J69" s="2" t="n">
-        <v>2.5</v>
+        <v>3.3</v>
       </c>
       <c r="K69" s="2" t="n">
-        <v>3.9</v>
+        <v>3.2</v>
       </c>
       <c r="L69" s="2" t="n">
-        <v>2.8</v>
+        <v>3</v>
       </c>
       <c r="M69" s="2" t="n">
-        <v>3.7</v>
+        <v>3.1</v>
       </c>
       <c r="N69" s="2" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="O69" s="2" t="n">
         <v>2.9</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
         <is>
-          <t>Wistron - Global</t>
+          <t>Pegatron - Fremont, CA</t>
         </is>
       </c>
       <c r="B70" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C70" s="2" t="inlineStr"/>
+          <t>Fremont, CA</t>
+        </is>
+      </c>
+      <c r="C70" s="2" t="inlineStr">
+        <is>
+          <t>United States</t>
+        </is>
+      </c>
       <c r="D70" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E70" s="2" t="n">
+          <t>Jeffersonville, IN</t>
+        </is>
+      </c>
+      <c r="E70" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/Pegatron-Jeffersonville-Reviews-EI_IE337948.0,8_IL.9,23_IC1145141.htm</t>
+        </is>
+      </c>
+      <c r="F70" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="G70" s="2" t="inlineStr">
+        <is>
+          <t>8%</t>
+        </is>
+      </c>
+      <c r="H70" s="2" t="inlineStr">
+        <is>
+          <t>2%</t>
+        </is>
+      </c>
+      <c r="I70" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="J70" s="2" t="n">
         <v>3.4</v>
       </c>
-      <c r="F70" s="2" t="inlineStr">
-        <is>
-          <t>48%</t>
-        </is>
-      </c>
-      <c r="G70" s="2" t="inlineStr">
-        <is>
-          <t>83%</t>
-        </is>
-      </c>
-      <c r="H70" s="2" t="inlineStr">
-        <is>
-          <t>710</t>
-        </is>
-      </c>
-      <c r="I70" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="J70" s="2" t="n">
-        <v>3.1</v>
-      </c>
       <c r="K70" s="2" t="n">
-        <v>2.8</v>
+        <v>2.2</v>
       </c>
       <c r="L70" s="2" t="n">
-        <v>3</v>
+        <v>1.9</v>
       </c>
       <c r="M70" s="2" t="n">
-        <v>3.1</v>
+        <v>2</v>
       </c>
       <c r="N70" s="2" t="n">
-        <v>2.7</v>
+        <v>1.3</v>
+      </c>
+      <c r="O70" s="2" t="n">
+        <v>1.4</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
         <is>
-          <t>Wistron - Taipei, TPQ</t>
+          <t>TSMC - Global</t>
         </is>
       </c>
       <c r="B71" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
-        </is>
-      </c>
-      <c r="C71" s="2" t="inlineStr">
-        <is>
-          <t>Taiwan</t>
-        </is>
-      </c>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="C71" s="2" t="inlineStr"/>
       <c r="D71" s="2" t="inlineStr">
         <is>
-          <t>Taipei, TPQ</t>
-        </is>
-      </c>
-      <c r="E71" s="2" t="n">
-        <v>3.6</v>
-      </c>
-      <c r="F71" s="2" t="inlineStr">
-        <is>
-          <t>66%</t>
-        </is>
+          <t>Global</t>
+        </is>
+      </c>
+      <c r="E71" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/TSMC-Reviews-E4130.htm</t>
+        </is>
+      </c>
+      <c r="F71" s="2" t="n">
+        <v>3.3</v>
       </c>
       <c r="G71" s="2" t="inlineStr">
         <is>
-          <t>95%</t>
+          <t>46%</t>
         </is>
       </c>
       <c r="H71" s="2" t="inlineStr">
         <is>
-          <t>216</t>
-        </is>
-      </c>
-      <c r="I71" s="2" t="n">
-        <v>3.3</v>
+          <t>74%</t>
+        </is>
+      </c>
+      <c r="I71" s="2" t="inlineStr">
+        <is>
+          <t>2,135</t>
+        </is>
       </c>
       <c r="J71" s="2" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="K71" s="2" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="L71" s="2" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="M71" s="2" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="N71" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="K71" s="2" t="n">
-        <v>3</v>
-      </c>
-      <c r="L71" s="2" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="M71" s="2" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="N71" s="2" t="n">
-        <v>2.9</v>
+      <c r="O71" s="2" t="n">
+        <v>2.7</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
         <is>
-          <t>Wiwynn - Global</t>
+          <t>TSMC - Taipei, TPQ</t>
         </is>
       </c>
       <c r="B72" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="C72" s="2" t="inlineStr"/>
+          <t>Taipei, TPQ</t>
+        </is>
+      </c>
+      <c r="C72" s="2" t="inlineStr">
+        <is>
+          <t>Taiwan</t>
+        </is>
+      </c>
       <c r="D72" s="2" t="inlineStr">
         <is>
-          <t>Global</t>
-        </is>
-      </c>
-      <c r="E72" s="2" t="n">
+          <t>Hsinchu, TXG</t>
+        </is>
+      </c>
+      <c r="E72" s="2" t="inlineStr">
+        <is>
+          <t>https://www.glassdoor.com/Reviews/TSMC-Hsinchu-Reviews-EI_IE4130.0,4_IL.5,12_IC4915323.htm</t>
+        </is>
+      </c>
+      <c r="F72" s="2" t="n">
         <v>3.5</v>
       </c>
-      <c r="F72" s="2" t="inlineStr">
-        <is>
-          <t>59%</t>
-        </is>
-      </c>
-      <c r="G72" s="2" t="inlineStr"/>
+      <c r="G72" s="2" t="inlineStr">
+        <is>
+          <t>52%</t>
+        </is>
+      </c>
       <c r="H72" s="2" t="inlineStr">
         <is>
-          <t>86</t>
-        </is>
-      </c>
-      <c r="I72" s="2" t="n">
-        <v>3.4</v>
+          <t>81%</t>
+        </is>
+      </c>
+      <c r="I72" s="2" t="inlineStr">
+        <is>
+          <t>613</t>
+        </is>
       </c>
       <c r="J72" s="2" t="n">
-        <v>3</v>
+        <v>2.9</v>
       </c>
       <c r="K72" s="2" t="n">
-        <v>3.5</v>
+        <v>2.5</v>
       </c>
       <c r="L72" s="2" t="n">
-        <v>3.1</v>
+        <v>3.9</v>
       </c>
       <c r="M72" s="2" t="n">
-        <v>3.5</v>
+        <v>2.8</v>
       </c>
       <c r="N72" s="2" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="O72" s="2" t="n">
         <v>2.9</v>
       </c>
     </row>
